--- a/premise/data/additional_inventories/lci-batteries-NMC622-NMC532.xlsx
+++ b/premise/data/additional_inventories/lci-batteries-NMC622-NMC532.xlsx
@@ -1164,15 +1164,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:ns4="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:X630"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" ns3:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="74.1640625" customWidth="1"/>
     <col min="2" max="2" width="42.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" ns3:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>192</v>
       </c>
@@ -1180,7 +1180,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
@@ -1188,7 +1188,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" ns3:dyDescent="0.2">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -1196,7 +1196,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" ns3:dyDescent="0.2">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1204,7 +1204,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" ns3:dyDescent="0.2">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -1212,7 +1212,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" ns3:dyDescent="0.2">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -1220,7 +1220,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" ns3:dyDescent="0.2">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -1228,12 +1228,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" ns3:dyDescent="0.2">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -1253,7 +1253,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>217</v>
       </c>
@@ -1273,7 +1273,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" ns3:dyDescent="0.2">
       <c r="A12" t="s">
         <v>57</v>
       </c>
@@ -1293,7 +1293,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" ns3:dyDescent="0.2">
       <c r="A13" t="s">
         <v>52</v>
       </c>
@@ -1313,7 +1313,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6" ns3:dyDescent="0.2">
       <c r="A14" t="s">
         <v>59</v>
       </c>
@@ -1333,7 +1333,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" ns3:dyDescent="0.2">
       <c r="A15" t="s">
         <v>218</v>
       </c>
@@ -1353,7 +1353,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" ns3:dyDescent="0.2">
       <c r="A16" t="s">
         <v>61</v>
       </c>
@@ -1373,7 +1373,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>215</v>
       </c>
@@ -1393,7 +1393,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>0</v>
       </c>
@@ -1401,7 +1401,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6" ns3:dyDescent="0.2">
       <c r="A20" t="s">
         <v>1</v>
       </c>
@@ -1409,7 +1409,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6" ns3:dyDescent="0.2">
       <c r="A21" t="s">
         <v>3</v>
       </c>
@@ -1417,7 +1417,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:6" ns3:dyDescent="0.2">
       <c r="A22" t="s">
         <v>5</v>
       </c>
@@ -1425,7 +1425,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:6" ns3:dyDescent="0.2">
       <c r="A23" t="s">
         <v>6</v>
       </c>
@@ -1433,7 +1433,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:6" ns3:dyDescent="0.2">
       <c r="A24" t="s">
         <v>7</v>
       </c>
@@ -1441,7 +1441,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:6" ns3:dyDescent="0.2">
       <c r="A25" t="s">
         <v>9</v>
       </c>
@@ -1449,12 +1449,12 @@
         <v>223</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:6" ns3:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:6" ns3:dyDescent="0.2">
       <c r="A27" t="s">
         <v>11</v>
       </c>
@@ -1474,7 +1474,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:6" ns3:dyDescent="0.2">
       <c r="A28" t="s">
         <v>215</v>
       </c>
@@ -1494,7 +1494,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:6" ns3:dyDescent="0.2">
       <c r="A29" t="s">
         <v>15</v>
       </c>
@@ -1514,7 +1514,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:6" ns3:dyDescent="0.2">
       <c r="A30" t="s">
         <v>18</v>
       </c>
@@ -1534,7 +1534,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:6" ns3:dyDescent="0.2">
       <c r="A31" t="s">
         <v>20</v>
       </c>
@@ -1554,7 +1554,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:6" ns3:dyDescent="0.2">
       <c r="A32" t="s">
         <v>22</v>
       </c>
@@ -1574,7 +1574,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:6" ns3:dyDescent="0.2">
       <c r="A33" t="s">
         <v>24</v>
       </c>
@@ -1594,7 +1594,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:6" ns3:dyDescent="0.2">
       <c r="A34" t="s">
         <v>26</v>
       </c>
@@ -1614,7 +1614,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:6" ns3:dyDescent="0.2">
       <c r="A35" t="s">
         <v>29</v>
       </c>
@@ -1634,7 +1634,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:6" ns3:dyDescent="0.2">
       <c r="A36" t="s">
         <v>31</v>
       </c>
@@ -1654,7 +1654,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:6" ns3:dyDescent="0.2">
       <c r="A37" t="s">
         <v>33</v>
       </c>
@@ -1674,7 +1674,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:6" ns3:dyDescent="0.2">
       <c r="A38" t="s">
         <v>35</v>
       </c>
@@ -1694,7 +1694,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:6" ns3:dyDescent="0.2">
       <c r="A39" t="s">
         <v>37</v>
       </c>
@@ -1714,7 +1714,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:6" ns3:dyDescent="0.2">
       <c r="A40" t="s">
         <v>39</v>
       </c>
@@ -1734,7 +1734,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:6" ns3:dyDescent="0.2">
       <c r="A41" t="s">
         <v>41</v>
       </c>
@@ -1754,7 +1754,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:6" ns3:dyDescent="0.2">
       <c r="A42" t="s">
         <v>43</v>
       </c>
@@ -1774,7 +1774,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:6" ns3:dyDescent="0.2">
       <c r="A43" t="s">
         <v>45</v>
       </c>
@@ -1794,7 +1794,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:6" ns3:dyDescent="0.2">
       <c r="A44" t="s">
         <v>48</v>
       </c>
@@ -1814,7 +1814,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:6" ns3:dyDescent="0.2">
       <c r="A45" t="s">
         <v>50</v>
       </c>
@@ -1834,7 +1834,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="47" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A47" s="2" t="s">
         <v>0</v>
       </c>
@@ -1842,7 +1842,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:6" ns3:dyDescent="0.2">
       <c r="A48" t="s">
         <v>1</v>
       </c>
@@ -1850,7 +1850,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:6" ns3:dyDescent="0.2">
       <c r="A49" t="s">
         <v>3</v>
       </c>
@@ -1858,7 +1858,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:6" ns3:dyDescent="0.2">
       <c r="A50" t="s">
         <v>5</v>
       </c>
@@ -1866,7 +1866,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:6" ns3:dyDescent="0.2">
       <c r="A51" t="s">
         <v>6</v>
       </c>
@@ -1874,7 +1874,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:6" ns3:dyDescent="0.2">
       <c r="A52" t="s">
         <v>7</v>
       </c>
@@ -1882,7 +1882,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:6" ns3:dyDescent="0.2">
       <c r="A53" t="s">
         <v>9</v>
       </c>
@@ -1890,12 +1890,12 @@
         <v>223</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:6" ns3:dyDescent="0.2">
       <c r="A54" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:6" ns3:dyDescent="0.2">
       <c r="A55" t="s">
         <v>11</v>
       </c>
@@ -1915,7 +1915,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:6" ns3:dyDescent="0.2">
       <c r="A56" t="s">
         <v>20</v>
       </c>
@@ -1935,7 +1935,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:6" ns3:dyDescent="0.2">
       <c r="A57" t="s">
         <v>52</v>
       </c>
@@ -1955,7 +1955,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:6" ns3:dyDescent="0.2">
       <c r="A58" t="s">
         <v>55</v>
       </c>
@@ -1975,7 +1975,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:6" ns3:dyDescent="0.2">
       <c r="A59" t="s">
         <v>57</v>
       </c>
@@ -1995,7 +1995,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:6" ns3:dyDescent="0.2">
       <c r="A60" t="s">
         <v>59</v>
       </c>
@@ -2015,7 +2015,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:6" ns3:dyDescent="0.2">
       <c r="A61" t="s">
         <v>61</v>
       </c>
@@ -2035,7 +2035,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:6" ns3:dyDescent="0.2">
       <c r="A62" t="s">
         <v>15</v>
       </c>
@@ -2055,7 +2055,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:6" ns3:dyDescent="0.2">
       <c r="A63" t="s">
         <v>39</v>
       </c>
@@ -2075,7 +2075,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:6" ns3:dyDescent="0.2">
       <c r="A64" t="s">
         <v>18</v>
       </c>
@@ -2095,7 +2095,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:6" ns3:dyDescent="0.2">
       <c r="A65" t="s">
         <v>33</v>
       </c>
@@ -2115,7 +2115,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:6" ns3:dyDescent="0.2">
       <c r="A66" t="s">
         <v>41</v>
       </c>
@@ -2135,7 +2135,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:6" ns3:dyDescent="0.2">
       <c r="A67" t="s">
         <v>43</v>
       </c>
@@ -2155,7 +2155,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:6" ns3:dyDescent="0.2">
       <c r="A68" t="s">
         <v>63</v>
       </c>
@@ -2175,7 +2175,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:6" ns3:dyDescent="0.2">
       <c r="A69" t="s">
         <v>37</v>
       </c>
@@ -2195,7 +2195,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:6" ns3:dyDescent="0.2">
       <c r="A70" t="s">
         <v>48</v>
       </c>
@@ -2215,7 +2215,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:6" ns3:dyDescent="0.2">
       <c r="A71" t="s">
         <v>50</v>
       </c>
@@ -2235,7 +2235,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="73" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A73" s="2" t="s">
         <v>0</v>
       </c>
@@ -2243,7 +2243,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:6" ns3:dyDescent="0.2">
       <c r="A74" t="s">
         <v>1</v>
       </c>
@@ -2251,7 +2251,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:6" ns3:dyDescent="0.2">
       <c r="A75" t="s">
         <v>3</v>
       </c>
@@ -2259,7 +2259,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:6" ns3:dyDescent="0.2">
       <c r="A76" t="s">
         <v>5</v>
       </c>
@@ -2267,7 +2267,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:6" ns3:dyDescent="0.2">
       <c r="A77" t="s">
         <v>6</v>
       </c>
@@ -2275,7 +2275,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:6" ns3:dyDescent="0.2">
       <c r="A78" t="s">
         <v>7</v>
       </c>
@@ -2283,7 +2283,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:6" ns3:dyDescent="0.2">
       <c r="A79" t="s">
         <v>9</v>
       </c>
@@ -2291,12 +2291,12 @@
         <v>223</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:6" ns3:dyDescent="0.2">
       <c r="A80" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:6" ns3:dyDescent="0.2">
       <c r="A81" t="s">
         <v>11</v>
       </c>
@@ -2316,7 +2316,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:6" ns3:dyDescent="0.2">
       <c r="A82" t="s">
         <v>22</v>
       </c>
@@ -2336,7 +2336,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:6" ns3:dyDescent="0.2">
       <c r="A83" t="s">
         <v>65</v>
       </c>
@@ -2356,7 +2356,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:6" ns3:dyDescent="0.2">
       <c r="A84" t="s">
         <v>67</v>
       </c>
@@ -2376,7 +2376,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:6" ns3:dyDescent="0.2">
       <c r="A85" t="s">
         <v>69</v>
       </c>
@@ -2396,7 +2396,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:6" ns3:dyDescent="0.2">
       <c r="A86" t="s">
         <v>70</v>
       </c>
@@ -2416,7 +2416,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:6" ns3:dyDescent="0.2">
       <c r="A87" t="s">
         <v>72</v>
       </c>
@@ -2436,7 +2436,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:6" ns3:dyDescent="0.2">
       <c r="A88" t="s">
         <v>74</v>
       </c>
@@ -2456,7 +2456,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:6" ns3:dyDescent="0.2">
       <c r="A89" t="s">
         <v>75</v>
       </c>
@@ -2476,7 +2476,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="91" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A91" s="2" t="s">
         <v>0</v>
       </c>
@@ -2484,7 +2484,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:6" ns3:dyDescent="0.2">
       <c r="A92" t="s">
         <v>1</v>
       </c>
@@ -2492,7 +2492,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:6" ns3:dyDescent="0.2">
       <c r="A93" t="s">
         <v>3</v>
       </c>
@@ -2500,7 +2500,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:6" ns3:dyDescent="0.2">
       <c r="A94" t="s">
         <v>5</v>
       </c>
@@ -2508,7 +2508,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:6" ns3:dyDescent="0.2">
       <c r="A95" t="s">
         <v>6</v>
       </c>
@@ -2516,7 +2516,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:6" ns3:dyDescent="0.2">
       <c r="A96" t="s">
         <v>7</v>
       </c>
@@ -2524,7 +2524,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:6" ns3:dyDescent="0.2">
       <c r="A97" t="s">
         <v>9</v>
       </c>
@@ -2532,12 +2532,12 @@
         <v>223</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:6" ns3:dyDescent="0.2">
       <c r="A98" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:6" ns3:dyDescent="0.2">
       <c r="A99" t="s">
         <v>11</v>
       </c>
@@ -2557,7 +2557,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:6" ns3:dyDescent="0.2">
       <c r="A100" t="s">
         <v>69</v>
       </c>
@@ -2577,7 +2577,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:6" ns3:dyDescent="0.2">
       <c r="A101" t="s">
         <v>15</v>
       </c>
@@ -2597,7 +2597,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:6" ns3:dyDescent="0.2">
       <c r="A102" t="s">
         <v>77</v>
       </c>
@@ -2617,7 +2617,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:6" ns3:dyDescent="0.2">
       <c r="A103" t="s">
         <v>35</v>
       </c>
@@ -2637,7 +2637,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:6" ns3:dyDescent="0.2">
       <c r="A104" t="s">
         <v>79</v>
       </c>
@@ -2657,7 +2657,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:6" ns3:dyDescent="0.2">
       <c r="A105" t="s">
         <v>81</v>
       </c>
@@ -2677,7 +2677,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:6" ns3:dyDescent="0.2">
       <c r="A106" t="s">
         <v>67</v>
       </c>
@@ -2697,7 +2697,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:6" ns3:dyDescent="0.2">
       <c r="A107" t="s">
         <v>83</v>
       </c>
@@ -2717,7 +2717,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:6" ns3:dyDescent="0.2">
       <c r="A108" t="s">
         <v>85</v>
       </c>
@@ -2737,7 +2737,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:6" ns3:dyDescent="0.2">
       <c r="A109" t="s">
         <v>87</v>
       </c>
@@ -2757,7 +2757,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:6" ns3:dyDescent="0.2">
       <c r="A110" t="s">
         <v>72</v>
       </c>
@@ -2777,7 +2777,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:6" ns3:dyDescent="0.2">
       <c r="A111" t="s">
         <v>70</v>
       </c>
@@ -2797,7 +2797,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:6" ns3:dyDescent="0.2">
       <c r="A112" t="s">
         <v>89</v>
       </c>
@@ -2817,7 +2817,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:6" ns3:dyDescent="0.2">
       <c r="A113" t="s">
         <v>91</v>
       </c>
@@ -2837,7 +2837,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:6" ns3:dyDescent="0.2">
       <c r="A114" t="s">
         <v>93</v>
       </c>
@@ -2857,7 +2857,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:6" ns3:dyDescent="0.2">
       <c r="A115" t="s">
         <v>95</v>
       </c>
@@ -2877,7 +2877,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:6" ns3:dyDescent="0.2">
       <c r="A116" t="s">
         <v>95</v>
       </c>
@@ -2897,7 +2897,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="118" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A118" s="2" t="s">
         <v>0</v>
       </c>
@@ -2905,7 +2905,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:6" ns3:dyDescent="0.2">
       <c r="A119" t="s">
         <v>1</v>
       </c>
@@ -2913,7 +2913,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:6" ns3:dyDescent="0.2">
       <c r="A120" t="s">
         <v>3</v>
       </c>
@@ -2921,7 +2921,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:6" ns3:dyDescent="0.2">
       <c r="A121" t="s">
         <v>5</v>
       </c>
@@ -2929,7 +2929,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:6" ns3:dyDescent="0.2">
       <c r="A122" t="s">
         <v>6</v>
       </c>
@@ -2937,7 +2937,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:6" ns3:dyDescent="0.2">
       <c r="A123" t="s">
         <v>7</v>
       </c>
@@ -2945,7 +2945,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:6" ns3:dyDescent="0.2">
       <c r="A124" t="s">
         <v>9</v>
       </c>
@@ -2953,12 +2953,12 @@
         <v>223</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:6" ns3:dyDescent="0.2">
       <c r="A125" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:6" ns3:dyDescent="0.2">
       <c r="A126" t="s">
         <v>11</v>
       </c>
@@ -2978,7 +2978,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:6" ns3:dyDescent="0.2">
       <c r="A127" t="s">
         <v>74</v>
       </c>
@@ -2998,7 +2998,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:6" ns3:dyDescent="0.2">
       <c r="A128" t="s">
         <v>70</v>
       </c>
@@ -3018,7 +3018,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:6" ns3:dyDescent="0.2">
       <c r="A129" t="s">
         <v>35</v>
       </c>
@@ -3038,7 +3038,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:6" ns3:dyDescent="0.2">
       <c r="A130" t="s">
         <v>33</v>
       </c>
@@ -3058,7 +3058,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:6" ns3:dyDescent="0.2">
       <c r="A131" t="s">
         <v>98</v>
       </c>
@@ -3078,7 +3078,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:6" ns3:dyDescent="0.2">
       <c r="A132" t="s">
         <v>98</v>
       </c>
@@ -3098,7 +3098,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="134" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A134" s="2" t="s">
         <v>0</v>
       </c>
@@ -3106,7 +3106,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:6" ns3:dyDescent="0.2">
       <c r="A135" t="s">
         <v>1</v>
       </c>
@@ -3114,7 +3114,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:6" ns3:dyDescent="0.2">
       <c r="A136" t="s">
         <v>3</v>
       </c>
@@ -3122,7 +3122,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:6" ns3:dyDescent="0.2">
       <c r="A137" t="s">
         <v>5</v>
       </c>
@@ -3130,7 +3130,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:6" ns3:dyDescent="0.2">
       <c r="A138" t="s">
         <v>6</v>
       </c>
@@ -3138,7 +3138,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:6" ns3:dyDescent="0.2">
       <c r="A139" t="s">
         <v>7</v>
       </c>
@@ -3146,7 +3146,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:6" ns3:dyDescent="0.2">
       <c r="A140" t="s">
         <v>9</v>
       </c>
@@ -3154,12 +3154,12 @@
         <v>100</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:6" ns3:dyDescent="0.2">
       <c r="A141" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:6" ns3:dyDescent="0.2">
       <c r="A142" t="s">
         <v>11</v>
       </c>
@@ -3179,7 +3179,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:6" ns3:dyDescent="0.2">
       <c r="A143" t="s">
         <v>65</v>
       </c>
@@ -3199,7 +3199,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:6" ns3:dyDescent="0.2">
       <c r="A144" t="s">
         <v>101</v>
       </c>
@@ -3219,7 +3219,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:6" ns3:dyDescent="0.2">
       <c r="A145" t="s">
         <v>72</v>
       </c>
@@ -3239,7 +3239,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:6" ns3:dyDescent="0.2">
       <c r="A146" t="s">
         <v>85</v>
       </c>
@@ -3259,7 +3259,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:6" ns3:dyDescent="0.2">
       <c r="A147" t="s">
         <v>103</v>
       </c>
@@ -3279,7 +3279,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:6" ns3:dyDescent="0.2">
       <c r="A148" t="s">
         <v>105</v>
       </c>
@@ -3299,7 +3299,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:6" ns3:dyDescent="0.2">
       <c r="A149" t="s">
         <v>35</v>
       </c>
@@ -3319,7 +3319,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:6" ns3:dyDescent="0.2">
       <c r="A150" t="s">
         <v>70</v>
       </c>
@@ -3339,7 +3339,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:6" ns3:dyDescent="0.2">
       <c r="A151" t="s">
         <v>107</v>
       </c>
@@ -3359,7 +3359,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:6" ns3:dyDescent="0.2">
       <c r="A152" t="s">
         <v>67</v>
       </c>
@@ -3379,7 +3379,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:6" ns3:dyDescent="0.2">
       <c r="A153" t="s">
         <v>75</v>
       </c>
@@ -3399,7 +3399,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:6" ns3:dyDescent="0.2">
       <c r="A154" t="s">
         <v>109</v>
       </c>
@@ -3419,7 +3419,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:6" ns3:dyDescent="0.2">
       <c r="A155" t="s">
         <v>109</v>
       </c>
@@ -3439,7 +3439,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:6" ns3:dyDescent="0.2">
       <c r="A156" t="s">
         <v>98</v>
       </c>
@@ -3459,7 +3459,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:6" ns3:dyDescent="0.2">
       <c r="A157" t="s">
         <v>98</v>
       </c>
@@ -3479,7 +3479,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="159" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A159" s="2" t="s">
         <v>0</v>
       </c>
@@ -3487,7 +3487,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:6" ns3:dyDescent="0.2">
       <c r="A160" t="s">
         <v>1</v>
       </c>
@@ -3495,7 +3495,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:7" ns3:dyDescent="0.2">
       <c r="A161" t="s">
         <v>3</v>
       </c>
@@ -3503,7 +3503,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:7" ns3:dyDescent="0.2">
       <c r="A162" t="s">
         <v>5</v>
       </c>
@@ -3511,7 +3511,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:7" ns3:dyDescent="0.2">
       <c r="A163" t="s">
         <v>6</v>
       </c>
@@ -3519,7 +3519,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:7" ns3:dyDescent="0.2">
       <c r="A164" t="s">
         <v>7</v>
       </c>
@@ -3527,7 +3527,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:7" ns3:dyDescent="0.2">
       <c r="A165" t="s">
         <v>9</v>
       </c>
@@ -3535,12 +3535,12 @@
         <v>223</v>
       </c>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:7" ns3:dyDescent="0.2">
       <c r="A166" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:7" ns3:dyDescent="0.2">
       <c r="A167" t="s">
         <v>11</v>
       </c>
@@ -3563,7 +3563,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:7" ns3:dyDescent="0.2">
       <c r="A168" t="s">
         <v>116</v>
       </c>
@@ -3583,7 +3583,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:7" ns3:dyDescent="0.2">
       <c r="A169" t="s">
         <v>122</v>
       </c>
@@ -3603,7 +3603,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:7" ns3:dyDescent="0.2">
       <c r="A170" t="s">
         <v>155</v>
       </c>
@@ -3623,7 +3623,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:7" ns3:dyDescent="0.2">
       <c r="A171" t="s">
         <v>157</v>
       </c>
@@ -3643,7 +3643,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:7" ns3:dyDescent="0.2">
       <c r="A172" t="s">
         <v>158</v>
       </c>
@@ -3663,7 +3663,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:7" ns3:dyDescent="0.2">
       <c r="A173" t="s">
         <v>45</v>
       </c>
@@ -3683,7 +3683,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:7" ns3:dyDescent="0.2">
       <c r="A174" t="s">
         <v>160</v>
       </c>
@@ -3703,7 +3703,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="176" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:7" ht="16" ns3:dyDescent="0.2">
       <c r="A176" s="2" t="s">
         <v>0</v>
       </c>
@@ -3711,7 +3711,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:7" ns3:dyDescent="0.2">
       <c r="A177" t="s">
         <v>1</v>
       </c>
@@ -3719,7 +3719,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:7" ns3:dyDescent="0.2">
       <c r="A178" t="s">
         <v>3</v>
       </c>
@@ -3727,7 +3727,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:7" ns3:dyDescent="0.2">
       <c r="A179" t="s">
         <v>5</v>
       </c>
@@ -3735,7 +3735,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:7" ns3:dyDescent="0.2">
       <c r="A180" t="s">
         <v>6</v>
       </c>
@@ -3743,7 +3743,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:7" ns3:dyDescent="0.2">
       <c r="A181" t="s">
         <v>7</v>
       </c>
@@ -3751,7 +3751,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:7" ns3:dyDescent="0.2">
       <c r="A182" t="s">
         <v>9</v>
       </c>
@@ -3759,12 +3759,12 @@
         <v>223</v>
       </c>
     </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:7" ns3:dyDescent="0.2">
       <c r="A183" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:7" ns3:dyDescent="0.2">
       <c r="A184" t="s">
         <v>11</v>
       </c>
@@ -3787,7 +3787,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:7" ns3:dyDescent="0.2">
       <c r="A185" t="s">
         <v>117</v>
       </c>
@@ -3807,7 +3807,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:7" ns3:dyDescent="0.2">
       <c r="A186" t="s">
         <v>59</v>
       </c>
@@ -3827,7 +3827,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:7" ns3:dyDescent="0.2">
       <c r="A187" t="s">
         <v>61</v>
       </c>
@@ -3847,7 +3847,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:7" ns3:dyDescent="0.2">
       <c r="A188" t="s">
         <v>52</v>
       </c>
@@ -3867,7 +3867,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:7" ns3:dyDescent="0.2">
       <c r="A189" t="s">
         <v>57</v>
       </c>
@@ -3887,7 +3887,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:7" ns3:dyDescent="0.2">
       <c r="A190" t="s">
         <v>55</v>
       </c>
@@ -3907,7 +3907,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:7" ns3:dyDescent="0.2">
       <c r="A191" t="s">
         <v>43</v>
       </c>
@@ -3927,7 +3927,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:7" ns3:dyDescent="0.2">
       <c r="A192" t="s">
         <v>50</v>
       </c>
@@ -3947,7 +3947,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:7" ns3:dyDescent="0.2">
       <c r="A193" t="s">
         <v>89</v>
       </c>
@@ -3967,7 +3967,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:7" ns3:dyDescent="0.2">
       <c r="A194" t="s">
         <v>141</v>
       </c>
@@ -3987,7 +3987,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:7" ns3:dyDescent="0.2">
       <c r="A195" t="s">
         <v>162</v>
       </c>
@@ -4007,7 +4007,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:7" ns3:dyDescent="0.2">
       <c r="A196" t="s">
         <v>162</v>
       </c>
@@ -4027,7 +4027,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:7" ns3:dyDescent="0.2">
       <c r="A197" t="s">
         <v>162</v>
       </c>
@@ -4047,7 +4047,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:7" ns3:dyDescent="0.2">
       <c r="A198" t="s">
         <v>165</v>
       </c>
@@ -4067,7 +4067,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:7" ns3:dyDescent="0.2">
       <c r="A199" t="s">
         <v>165</v>
       </c>
@@ -4087,7 +4087,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="201" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:7" ht="16" ns3:dyDescent="0.2">
       <c r="A201" s="2" t="s">
         <v>0</v>
       </c>
@@ -4095,7 +4095,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:7" ns3:dyDescent="0.2">
       <c r="A202" t="s">
         <v>1</v>
       </c>
@@ -4103,7 +4103,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:7" ns3:dyDescent="0.2">
       <c r="A203" t="s">
         <v>3</v>
       </c>
@@ -4111,7 +4111,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:7" ns3:dyDescent="0.2">
       <c r="A204" t="s">
         <v>5</v>
       </c>
@@ -4119,7 +4119,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:7" ns3:dyDescent="0.2">
       <c r="A205" t="s">
         <v>6</v>
       </c>
@@ -4127,7 +4127,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:7" ns3:dyDescent="0.2">
       <c r="A206" t="s">
         <v>7</v>
       </c>
@@ -4135,7 +4135,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:7" ns3:dyDescent="0.2">
       <c r="A207" t="s">
         <v>9</v>
       </c>
@@ -4143,12 +4143,12 @@
         <v>223</v>
       </c>
     </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:7" ns3:dyDescent="0.2">
       <c r="A208" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:7" ns3:dyDescent="0.2">
       <c r="A209" t="s">
         <v>11</v>
       </c>
@@ -4171,7 +4171,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:7" ns3:dyDescent="0.2">
       <c r="A210" t="s">
         <v>118</v>
       </c>
@@ -4191,7 +4191,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:7" ns3:dyDescent="0.2">
       <c r="A211" t="s">
         <v>55</v>
       </c>
@@ -4211,7 +4211,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:7" ns3:dyDescent="0.2">
       <c r="A212" t="s">
         <v>61</v>
       </c>
@@ -4231,7 +4231,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:7" ns3:dyDescent="0.2">
       <c r="A213" t="s">
         <v>52</v>
       </c>
@@ -4251,7 +4251,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:7" ns3:dyDescent="0.2">
       <c r="A214" t="s">
         <v>57</v>
       </c>
@@ -4271,7 +4271,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:7" ns3:dyDescent="0.2">
       <c r="A215" t="s">
         <v>59</v>
       </c>
@@ -4291,7 +4291,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:7" ns3:dyDescent="0.2">
       <c r="A216" t="s">
         <v>141</v>
       </c>
@@ -4311,7 +4311,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:7" ns3:dyDescent="0.2">
       <c r="A217" t="s">
         <v>15</v>
       </c>
@@ -4331,7 +4331,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:7" ns3:dyDescent="0.2">
       <c r="A218" t="s">
         <v>39</v>
       </c>
@@ -4351,7 +4351,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:7" ns3:dyDescent="0.2">
       <c r="A219" t="s">
         <v>167</v>
       </c>
@@ -4371,7 +4371,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:7" ns3:dyDescent="0.2">
       <c r="A220" t="s">
         <v>162</v>
       </c>
@@ -4391,7 +4391,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:7" ns3:dyDescent="0.2">
       <c r="A221" t="s">
         <v>162</v>
       </c>
@@ -4411,7 +4411,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:7" ns3:dyDescent="0.2">
       <c r="A222" t="s">
         <v>162</v>
       </c>
@@ -4431,7 +4431,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:7" ns3:dyDescent="0.2">
       <c r="A223" t="s">
         <v>165</v>
       </c>
@@ -4451,7 +4451,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:7" ns3:dyDescent="0.2">
       <c r="A224" t="s">
         <v>165</v>
       </c>
@@ -4471,7 +4471,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="226" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:7" ht="16" ns3:dyDescent="0.2">
       <c r="A226" s="2" t="s">
         <v>0</v>
       </c>
@@ -4479,7 +4479,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:7" ns3:dyDescent="0.2">
       <c r="A227" t="s">
         <v>1</v>
       </c>
@@ -4487,7 +4487,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:7" ns3:dyDescent="0.2">
       <c r="A228" t="s">
         <v>3</v>
       </c>
@@ -4495,7 +4495,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:7" ns3:dyDescent="0.2">
       <c r="A229" t="s">
         <v>5</v>
       </c>
@@ -4503,7 +4503,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:7" ns3:dyDescent="0.2">
       <c r="A230" t="s">
         <v>6</v>
       </c>
@@ -4511,7 +4511,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:7" ns3:dyDescent="0.2">
       <c r="A231" t="s">
         <v>7</v>
       </c>
@@ -4519,7 +4519,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:7" ns3:dyDescent="0.2">
       <c r="A232" t="s">
         <v>9</v>
       </c>
@@ -4527,12 +4527,12 @@
         <v>223</v>
       </c>
     </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:7" ns3:dyDescent="0.2">
       <c r="A233" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:7" ns3:dyDescent="0.2">
       <c r="A234" t="s">
         <v>11</v>
       </c>
@@ -4555,7 +4555,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:7" ns3:dyDescent="0.2">
       <c r="A235" t="s">
         <v>119</v>
       </c>
@@ -4575,7 +4575,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:7" ns3:dyDescent="0.2">
       <c r="A236" t="s">
         <v>59</v>
       </c>
@@ -4595,7 +4595,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:7" ns3:dyDescent="0.2">
       <c r="A237" t="s">
         <v>55</v>
       </c>
@@ -4615,7 +4615,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:7" ns3:dyDescent="0.2">
       <c r="A238" t="s">
         <v>63</v>
       </c>
@@ -4635,7 +4635,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="239" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:7" ns3:dyDescent="0.2">
       <c r="A239" t="s">
         <v>37</v>
       </c>
@@ -4655,7 +4655,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="240" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:7" ns3:dyDescent="0.2">
       <c r="A240" t="s">
         <v>169</v>
       </c>
@@ -4675,7 +4675,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="241" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:7" ns3:dyDescent="0.2">
       <c r="A241" t="s">
         <v>171</v>
       </c>
@@ -4695,7 +4695,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:7" ns3:dyDescent="0.2">
       <c r="A242" t="s">
         <v>112</v>
       </c>
@@ -4715,7 +4715,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="243" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:7" ns3:dyDescent="0.2">
       <c r="A243" t="s">
         <v>127</v>
       </c>
@@ -4735,7 +4735,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="244" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:7" ns3:dyDescent="0.2">
       <c r="A244" t="s">
         <v>173</v>
       </c>
@@ -4755,7 +4755,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="245" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:7" ns3:dyDescent="0.2">
       <c r="A245" t="s">
         <v>175</v>
       </c>
@@ -4775,7 +4775,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="246" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:7" ns3:dyDescent="0.2">
       <c r="A246" t="s">
         <v>45</v>
       </c>
@@ -4795,7 +4795,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="247" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:7" ns3:dyDescent="0.2">
       <c r="A247" t="s">
         <v>122</v>
       </c>
@@ -4815,7 +4815,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="248" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:7" ns3:dyDescent="0.2">
       <c r="A248" t="s">
         <v>177</v>
       </c>
@@ -4835,7 +4835,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="250" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:7" ht="16" ns3:dyDescent="0.2">
       <c r="A250" s="2" t="s">
         <v>0</v>
       </c>
@@ -4843,7 +4843,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="251" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:7" ns3:dyDescent="0.2">
       <c r="A251" t="s">
         <v>1</v>
       </c>
@@ -4851,7 +4851,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="252" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:7" ns3:dyDescent="0.2">
       <c r="A252" t="s">
         <v>3</v>
       </c>
@@ -4859,7 +4859,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="253" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:7" ns3:dyDescent="0.2">
       <c r="A253" t="s">
         <v>5</v>
       </c>
@@ -4867,7 +4867,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="254" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:7" ht="16" ns3:dyDescent="0.2">
       <c r="A254" t="s">
         <v>6</v>
       </c>
@@ -4875,7 +4875,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="255" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:7" ns3:dyDescent="0.2">
       <c r="A255" t="s">
         <v>7</v>
       </c>
@@ -4883,12 +4883,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="256" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:7" ht="16" ns3:dyDescent="0.2">
       <c r="A256" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="257" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:6" ns3:dyDescent="0.2">
       <c r="A257" t="s">
         <v>11</v>
       </c>
@@ -4908,7 +4908,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="258" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A258" s="3" t="s">
         <v>219</v>
       </c>
@@ -4928,7 +4928,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="259" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:6" ns3:dyDescent="0.2">
       <c r="A259" t="s">
         <v>57</v>
       </c>
@@ -4948,7 +4948,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="260" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:6" ns3:dyDescent="0.2">
       <c r="A260" t="s">
         <v>52</v>
       </c>
@@ -4968,7 +4968,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="261" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:6" ns3:dyDescent="0.2">
       <c r="A261" t="s">
         <v>59</v>
       </c>
@@ -4988,7 +4988,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="262" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:6" ns3:dyDescent="0.2">
       <c r="A262" t="s">
         <v>218</v>
       </c>
@@ -5008,7 +5008,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="263" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:6" ns3:dyDescent="0.2">
       <c r="A263" t="s">
         <v>61</v>
       </c>
@@ -5028,7 +5028,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="264" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A264" s="3" t="s">
         <v>211</v>
       </c>
@@ -5048,7 +5048,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="266" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A266" s="2" t="s">
         <v>0</v>
       </c>
@@ -5056,7 +5056,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="267" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:6" ns3:dyDescent="0.2">
       <c r="A267" t="s">
         <v>1</v>
       </c>
@@ -5064,7 +5064,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="268" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:6" ns3:dyDescent="0.2">
       <c r="A268" t="s">
         <v>3</v>
       </c>
@@ -5072,7 +5072,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="269" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:6" ns3:dyDescent="0.2">
       <c r="A269" t="s">
         <v>5</v>
       </c>
@@ -5080,7 +5080,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="270" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A270" t="s">
         <v>6</v>
       </c>
@@ -5088,7 +5088,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="271" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:6" ns3:dyDescent="0.2">
       <c r="A271" t="s">
         <v>7</v>
       </c>
@@ -5096,12 +5096,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="272" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A272" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="273" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:6" ns3:dyDescent="0.2">
       <c r="A273" t="s">
         <v>11</v>
       </c>
@@ -5121,7 +5121,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="274" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A274" s="3" t="str">
         <f>B266</f>
         <v>market for battery, Li-ion, NMC622</v>
@@ -5143,7 +5143,7 @@
         <v>battery, Li-ion, NMC622</v>
       </c>
     </row>
-    <row r="275" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A275" s="3" t="s">
         <v>227</v>
       </c>
@@ -5163,7 +5163,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="276" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:6" ns3:dyDescent="0.2">
       <c r="A276" t="s">
         <v>59</v>
       </c>
@@ -5183,7 +5183,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="277" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:6" ns3:dyDescent="0.2">
       <c r="A277" t="s">
         <v>57</v>
       </c>
@@ -5203,7 +5203,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="278" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:6" ns3:dyDescent="0.2">
       <c r="A278" t="s">
         <v>218</v>
       </c>
@@ -5223,7 +5223,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="279" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:6" ns3:dyDescent="0.2">
       <c r="A279" t="s">
         <v>61</v>
       </c>
@@ -5243,7 +5243,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="281" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A281" s="2" t="s">
         <v>0</v>
       </c>
@@ -5251,7 +5251,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="282" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:6" ns3:dyDescent="0.2">
       <c r="A282" t="s">
         <v>1</v>
       </c>
@@ -5259,7 +5259,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="283" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:6" ns3:dyDescent="0.2">
       <c r="A283" t="s">
         <v>3</v>
       </c>
@@ -5267,7 +5267,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="284" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:6" ns3:dyDescent="0.2">
       <c r="A284" t="s">
         <v>5</v>
       </c>
@@ -5275,7 +5275,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="285" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A285" t="s">
         <v>6</v>
       </c>
@@ -5283,7 +5283,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="286" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:6" ns3:dyDescent="0.2">
       <c r="A286" t="s">
         <v>7</v>
       </c>
@@ -5291,12 +5291,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="287" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A287" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="288" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:6" ns3:dyDescent="0.2">
       <c r="A288" t="s">
         <v>11</v>
       </c>
@@ -5316,7 +5316,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="289" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A289" s="3" t="str">
         <f>B281</f>
         <v>battery production, Li-ion, NMC622</v>
@@ -5338,7 +5338,7 @@
         <v>battery, Li-ion, NMC622</v>
       </c>
     </row>
-    <row r="290" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:6" ns3:dyDescent="0.2">
       <c r="A290" t="s">
         <v>15</v>
       </c>
@@ -5358,7 +5358,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="291" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:6" ns3:dyDescent="0.2">
       <c r="A291" t="s">
         <v>211</v>
       </c>
@@ -5378,7 +5378,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="292" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:6" ns3:dyDescent="0.2">
       <c r="A292" t="s">
         <v>215</v>
       </c>
@@ -5398,7 +5398,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="293" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:6" ns3:dyDescent="0.2">
       <c r="A293" t="s">
         <v>228</v>
       </c>
@@ -5418,7 +5418,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="294" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:6" ns3:dyDescent="0.2">
       <c r="A294" t="s">
         <v>41</v>
       </c>
@@ -5438,7 +5438,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="295" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:6" ns3:dyDescent="0.2">
       <c r="A295" t="s">
         <v>45</v>
       </c>
@@ -5458,7 +5458,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="296" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:6" ns3:dyDescent="0.2">
       <c r="A296" t="s">
         <v>33</v>
       </c>
@@ -5478,7 +5478,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="297" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:6" ns3:dyDescent="0.2">
       <c r="A297" t="s">
         <v>24</v>
       </c>
@@ -5498,7 +5498,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="298" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:6" ns3:dyDescent="0.2">
       <c r="A298" t="s">
         <v>48</v>
       </c>
@@ -5518,7 +5518,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="299" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:6" ns3:dyDescent="0.2">
       <c r="A299" t="s">
         <v>18</v>
       </c>
@@ -5538,7 +5538,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="300" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:6" ns3:dyDescent="0.2">
       <c r="A300" t="s">
         <v>35</v>
       </c>
@@ -5558,7 +5558,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="301" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:6" ns3:dyDescent="0.2">
       <c r="A301" t="s">
         <v>50</v>
       </c>
@@ -5578,7 +5578,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="302" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:6" ns3:dyDescent="0.2">
       <c r="A302" t="s">
         <v>37</v>
       </c>
@@ -5598,7 +5598,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="303" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:6" ns3:dyDescent="0.2">
       <c r="A303" t="s">
         <v>29</v>
       </c>
@@ -5618,7 +5618,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="304" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:6" ns3:dyDescent="0.2">
       <c r="A304" t="s">
         <v>39</v>
       </c>
@@ -5638,7 +5638,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="305" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:6" ns3:dyDescent="0.2">
       <c r="A305" t="s">
         <v>43</v>
       </c>
@@ -5658,7 +5658,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="306" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:6" ns3:dyDescent="0.2">
       <c r="A306" t="s">
         <v>31</v>
       </c>
@@ -5678,7 +5678,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="307" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:6" ns3:dyDescent="0.2">
       <c r="A307" t="s">
         <v>26</v>
       </c>
@@ -5698,7 +5698,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="309" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A309" s="2" t="s">
         <v>0</v>
       </c>
@@ -5706,7 +5706,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="310" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:6" ns3:dyDescent="0.2">
       <c r="A310" t="s">
         <v>1</v>
       </c>
@@ -5714,7 +5714,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="311" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:6" ns3:dyDescent="0.2">
       <c r="A311" t="s">
         <v>3</v>
       </c>
@@ -5722,7 +5722,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="312" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:6" ns3:dyDescent="0.2">
       <c r="A312" t="s">
         <v>5</v>
       </c>
@@ -5730,7 +5730,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="313" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A313" t="s">
         <v>6</v>
       </c>
@@ -5738,7 +5738,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="314" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:6" ns3:dyDescent="0.2">
       <c r="A314" t="s">
         <v>7</v>
       </c>
@@ -5746,12 +5746,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="315" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A315" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="316" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:6" ns3:dyDescent="0.2">
       <c r="A316" t="s">
         <v>11</v>
       </c>
@@ -5771,7 +5771,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="317" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A317" s="3" t="str">
         <f>B309</f>
         <v>market for battery, Li-ion, NMC532</v>
@@ -5793,7 +5793,7 @@
         <v>battery, Li-ion, NMC532</v>
       </c>
     </row>
-    <row r="318" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A318" s="9" t="s">
         <v>232</v>
       </c>
@@ -5813,7 +5813,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="319" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:6" ns3:dyDescent="0.2">
       <c r="A319" t="s">
         <v>59</v>
       </c>
@@ -5833,7 +5833,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="320" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:6" ns3:dyDescent="0.2">
       <c r="A320" t="s">
         <v>57</v>
       </c>
@@ -5853,7 +5853,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="321" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:6" ns3:dyDescent="0.2">
       <c r="A321" t="s">
         <v>218</v>
       </c>
@@ -5873,7 +5873,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="322" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:6" ns3:dyDescent="0.2">
       <c r="A322" t="s">
         <v>61</v>
       </c>
@@ -5893,7 +5893,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="324" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A324" s="2" t="s">
         <v>0</v>
       </c>
@@ -5901,7 +5901,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="325" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:6" ns3:dyDescent="0.2">
       <c r="A325" t="s">
         <v>1</v>
       </c>
@@ -5909,7 +5909,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="326" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:6" ns3:dyDescent="0.2">
       <c r="A326" t="s">
         <v>3</v>
       </c>
@@ -5917,7 +5917,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="327" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:6" ns3:dyDescent="0.2">
       <c r="A327" t="s">
         <v>5</v>
       </c>
@@ -5925,7 +5925,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="328" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A328" t="s">
         <v>6</v>
       </c>
@@ -5933,7 +5933,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="329" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:6" ns3:dyDescent="0.2">
       <c r="A329" t="s">
         <v>7</v>
       </c>
@@ -5941,12 +5941,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="330" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A330" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="331" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:6" ns3:dyDescent="0.2">
       <c r="A331" t="s">
         <v>11</v>
       </c>
@@ -5966,7 +5966,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="332" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A332" s="3" t="str">
         <f>B324</f>
         <v>battery production, Li-ion, NMC532</v>
@@ -5988,7 +5988,7 @@
         <v>battery, Li-ion, NMC532</v>
       </c>
     </row>
-    <row r="333" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:6" ns3:dyDescent="0.2">
       <c r="A333" t="s">
         <v>15</v>
       </c>
@@ -6008,7 +6008,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="334" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:6" ns3:dyDescent="0.2">
       <c r="A334" t="s">
         <v>233</v>
       </c>
@@ -6028,7 +6028,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="335" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:6" ns3:dyDescent="0.2">
       <c r="A335" t="s">
         <v>215</v>
       </c>
@@ -6048,7 +6048,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="336" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:6" ns3:dyDescent="0.2">
       <c r="A336" t="s">
         <v>228</v>
       </c>
@@ -6068,7 +6068,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="337" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:6" ns3:dyDescent="0.2">
       <c r="A337" t="s">
         <v>41</v>
       </c>
@@ -6088,7 +6088,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="338" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:6" ns3:dyDescent="0.2">
       <c r="A338" t="s">
         <v>45</v>
       </c>
@@ -6108,7 +6108,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="339" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:6" ns3:dyDescent="0.2">
       <c r="A339" t="s">
         <v>33</v>
       </c>
@@ -6128,7 +6128,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="340" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:6" ns3:dyDescent="0.2">
       <c r="A340" t="s">
         <v>24</v>
       </c>
@@ -6148,7 +6148,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="341" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:6" ns3:dyDescent="0.2">
       <c r="A341" t="s">
         <v>48</v>
       </c>
@@ -6168,7 +6168,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="342" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:6" ns3:dyDescent="0.2">
       <c r="A342" t="s">
         <v>18</v>
       </c>
@@ -6188,7 +6188,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="343" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:6" ns3:dyDescent="0.2">
       <c r="A343" t="s">
         <v>35</v>
       </c>
@@ -6208,7 +6208,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="344" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:6" ns3:dyDescent="0.2">
       <c r="A344" t="s">
         <v>50</v>
       </c>
@@ -6228,7 +6228,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="345" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:6" ns3:dyDescent="0.2">
       <c r="A345" t="s">
         <v>37</v>
       </c>
@@ -6248,7 +6248,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="346" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:6" ns3:dyDescent="0.2">
       <c r="A346" t="s">
         <v>29</v>
       </c>
@@ -6268,7 +6268,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="347" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:6" ns3:dyDescent="0.2">
       <c r="A347" t="s">
         <v>39</v>
       </c>
@@ -6288,7 +6288,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="348" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:6" ns3:dyDescent="0.2">
       <c r="A348" t="s">
         <v>43</v>
       </c>
@@ -6308,7 +6308,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="349" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:6" ns3:dyDescent="0.2">
       <c r="A349" t="s">
         <v>31</v>
       </c>
@@ -6328,7 +6328,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="350" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:6" ns3:dyDescent="0.2">
       <c r="A350" t="s">
         <v>26</v>
       </c>
@@ -6348,7 +6348,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="352" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A352" s="2" t="s">
         <v>0</v>
       </c>
@@ -6356,15 +6356,17 @@
         <v>211</v>
       </c>
     </row>
-    <row r="353" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:6" ns3:dyDescent="0.2">
       <c r="A353" t="s">
         <v>1</v>
       </c>
-      <c r="B353" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="354" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>NMC622 cathode balance v1. Dai et al. 2018, Update of Bill-of-Materials and Cathode Materials Production for Lithium-ion Batteries in the GREET Model, Table 8 (BEV NMC622, 108.03 kg cell), https://greet.anl.gov/files/update_bom_cm. Cathode-specific binder and foil split follows the documented parent-cell breakdown: 35.01 kg active oxide, 2.36 kg carbon black, 2.07 kg binder, 5.89 kg aluminium current collector. This supplemental inventory represents dry cathode paste and its aluminium collector as separate cell inputs; their combined mass is 45.33/108.03 kg/kg cell. The correction selects that documented cathode subsystem, not a complete reconstruction of the Dai cell. Other cell ingredients, assembly energy, pack/capacity allocation and future density assumptions remain inherited and unvalidated. The remaining cell material budget is not renormalized. This workbook is skipped by the existing default import rules for ecoinvent 3.11 and 3.12; editing it alone does not correct the native cathode recipes in those versions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="354" spans="1:6" ns3:dyDescent="0.2">
       <c r="A354" t="s">
         <v>3</v>
       </c>
@@ -6372,7 +6374,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="355" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:6" ns3:dyDescent="0.2">
       <c r="A355" t="s">
         <v>5</v>
       </c>
@@ -6380,7 +6382,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="356" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A356" t="s">
         <v>6</v>
       </c>
@@ -6388,7 +6390,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="357" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:6" ns3:dyDescent="0.2">
       <c r="A357" t="s">
         <v>7</v>
       </c>
@@ -6396,7 +6398,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="358" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:6" ns3:dyDescent="0.2">
       <c r="A358" t="s">
         <v>9</v>
       </c>
@@ -6404,12 +6406,12 @@
         <v>224</v>
       </c>
     </row>
-    <row r="359" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:6" ns3:dyDescent="0.2">
       <c r="A359" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="360" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:6" ns3:dyDescent="0.2">
       <c r="A360" t="s">
         <v>11</v>
       </c>
@@ -6428,8 +6430,13 @@
       <c r="F360" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="361" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="361" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A361" t="s">
         <v>211</v>
       </c>
@@ -6449,7 +6456,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="362" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:6" ns3:dyDescent="0.2">
       <c r="A362" t="s">
         <v>112</v>
       </c>
@@ -6469,7 +6476,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="363" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:6" ns3:dyDescent="0.2">
       <c r="A363" t="s">
         <v>45</v>
       </c>
@@ -6489,12 +6496,12 @@
         <v>47</v>
       </c>
     </row>
-    <row r="364" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:6" ns3:dyDescent="0.2">
       <c r="A364" t="s">
         <v>212</v>
       </c>
       <c r="B364" s="4">
-        <v>0.41</v>
+        <v>0.36508377302601125</v>
       </c>
       <c r="C364" t="s">
         <v>8</v>
@@ -6508,8 +6515,13 @@
       <c r="F364" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="365" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>NMC622 cathode balance v1. Dry paste only: (35.01+2.36+2.07)/108.03 = 0.36508377302601125 kg/kg cell. The aluminium collector is bought separately by this cell. Dai et al. 2018, Update of Bill-of-Materials and Cathode Materials Production for Lithium-ion Batteries in the GREET Model, Table 8 (BEV NMC622, 108.03 kg cell), https://greet.anl.gov/files/update_bom_cm. Cathode-specific binder and foil split follows the documented parent-cell breakdown: 35.01 kg active oxide, 2.36 kg carbon black, 2.07 kg binder, 5.89 kg aluminium current collector.</t>
+        </is>
+      </c>
+    </row>
+    <row r="365" spans="1:6" ns3:dyDescent="0.2">
       <c r="A365" t="s">
         <v>226</v>
       </c>
@@ -6529,7 +6541,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="366" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:6" ns3:dyDescent="0.2">
       <c r="A366" t="s">
         <v>116</v>
       </c>
@@ -6549,7 +6561,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="367" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:6" ns3:dyDescent="0.2">
       <c r="A367" t="s">
         <v>117</v>
       </c>
@@ -6569,7 +6581,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="368" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:6" ns3:dyDescent="0.2">
       <c r="A368" t="s">
         <v>43</v>
       </c>
@@ -6589,7 +6601,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="369" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:6" ns3:dyDescent="0.2">
       <c r="A369" t="s">
         <v>41</v>
       </c>
@@ -6609,12 +6621,12 @@
         <v>42</v>
       </c>
     </row>
-    <row r="370" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:6" ns3:dyDescent="0.2">
       <c r="A370" t="s">
         <v>118</v>
       </c>
       <c r="B370" s="4">
-        <v>0.03</v>
+        <v>0.054521892067018414</v>
       </c>
       <c r="C370" t="s">
         <v>8</v>
@@ -6628,8 +6640,13 @@
       <c r="F370" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="371" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>NMC622 cathode balance v1. Separate cathode aluminium collector: 5.89/108.03 = 0.054521892067018414 kg/kg cell. The linked paste contains no foil. Dai et al. 2018, Update of Bill-of-Materials and Cathode Materials Production for Lithium-ion Batteries in the GREET Model, Table 8 (BEV NMC622, 108.03 kg cell), https://greet.anl.gov/files/update_bom_cm. Cathode-specific binder and foil split follows the documented parent-cell breakdown: 35.01 kg active oxide, 2.36 kg carbon black, 2.07 kg binder, 5.89 kg aluminium current collector.</t>
+        </is>
+      </c>
+    </row>
+    <row r="371" spans="1:6" ns3:dyDescent="0.2">
       <c r="A371" t="s">
         <v>15</v>
       </c>
@@ -6649,7 +6666,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="372" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:6" ns3:dyDescent="0.2">
       <c r="A372" t="s">
         <v>39</v>
       </c>
@@ -6669,7 +6686,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="373" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:6" ns3:dyDescent="0.2">
       <c r="A373" t="s">
         <v>119</v>
       </c>
@@ -6689,7 +6706,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="374" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:6" ns3:dyDescent="0.2">
       <c r="A374" t="s">
         <v>63</v>
       </c>
@@ -6709,7 +6726,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="375" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:6" ns3:dyDescent="0.2">
       <c r="A375" t="s">
         <v>85</v>
       </c>
@@ -6729,7 +6746,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="376" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:6" ns3:dyDescent="0.2">
       <c r="A376" t="s">
         <v>120</v>
       </c>
@@ -6749,7 +6766,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="377" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:6" ns3:dyDescent="0.2">
       <c r="A377" t="s">
         <v>122</v>
       </c>
@@ -6769,7 +6786,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="379" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A379" s="2" t="s">
         <v>0</v>
       </c>
@@ -6777,7 +6794,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="380" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:6" ns3:dyDescent="0.2">
       <c r="A380" t="s">
         <v>1</v>
       </c>
@@ -6785,7 +6802,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="381" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:6" ns3:dyDescent="0.2">
       <c r="A381" t="s">
         <v>3</v>
       </c>
@@ -6793,7 +6810,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="382" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:6" ns3:dyDescent="0.2">
       <c r="A382" t="s">
         <v>5</v>
       </c>
@@ -6801,7 +6818,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="383" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A383" t="s">
         <v>6</v>
       </c>
@@ -6809,7 +6826,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="384" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:6" ns3:dyDescent="0.2">
       <c r="A384" t="s">
         <v>7</v>
       </c>
@@ -6817,7 +6834,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="385" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:6" ns3:dyDescent="0.2">
       <c r="A385" t="s">
         <v>9</v>
       </c>
@@ -6825,12 +6842,12 @@
         <v>235</v>
       </c>
     </row>
-    <row r="386" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:6" ns3:dyDescent="0.2">
       <c r="A386" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="387" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:6" ns3:dyDescent="0.2">
       <c r="A387" t="s">
         <v>11</v>
       </c>
@@ -6850,7 +6867,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="388" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A388" t="s">
         <v>233</v>
       </c>
@@ -6870,7 +6887,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="389" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:6" ns3:dyDescent="0.2">
       <c r="A389" t="s">
         <v>112</v>
       </c>
@@ -6890,7 +6907,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="390" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:6" ns3:dyDescent="0.2">
       <c r="A390" t="s">
         <v>45</v>
       </c>
@@ -6910,7 +6927,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="391" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:6" ns3:dyDescent="0.2">
       <c r="A391" t="s">
         <v>236</v>
       </c>
@@ -6930,7 +6947,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="392" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:6" ns3:dyDescent="0.2">
       <c r="A392" t="s">
         <v>226</v>
       </c>
@@ -6950,7 +6967,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="393" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:6" ns3:dyDescent="0.2">
       <c r="A393" t="s">
         <v>116</v>
       </c>
@@ -6970,7 +6987,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="394" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:6" ns3:dyDescent="0.2">
       <c r="A394" t="s">
         <v>117</v>
       </c>
@@ -6990,7 +7007,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="395" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:6" ns3:dyDescent="0.2">
       <c r="A395" t="s">
         <v>43</v>
       </c>
@@ -7010,7 +7027,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="396" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:6" ns3:dyDescent="0.2">
       <c r="A396" t="s">
         <v>41</v>
       </c>
@@ -7030,7 +7047,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="397" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:6" ns3:dyDescent="0.2">
       <c r="A397" t="s">
         <v>118</v>
       </c>
@@ -7050,7 +7067,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="398" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:6" ns3:dyDescent="0.2">
       <c r="A398" t="s">
         <v>15</v>
       </c>
@@ -7070,7 +7087,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="399" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:6" ns3:dyDescent="0.2">
       <c r="A399" t="s">
         <v>39</v>
       </c>
@@ -7090,7 +7107,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="400" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:6" ns3:dyDescent="0.2">
       <c r="A400" t="s">
         <v>119</v>
       </c>
@@ -7110,7 +7127,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="401" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:6" ns3:dyDescent="0.2">
       <c r="A401" t="s">
         <v>63</v>
       </c>
@@ -7130,7 +7147,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="402" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:6" ns3:dyDescent="0.2">
       <c r="A402" t="s">
         <v>85</v>
       </c>
@@ -7150,7 +7167,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="403" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:6" ns3:dyDescent="0.2">
       <c r="A403" t="s">
         <v>120</v>
       </c>
@@ -7170,7 +7187,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="404" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:6" ns3:dyDescent="0.2">
       <c r="A404" t="s">
         <v>122</v>
       </c>
@@ -7190,7 +7207,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="406" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A406" s="2" t="s">
         <v>0</v>
       </c>
@@ -7198,15 +7215,17 @@
         <v>212</v>
       </c>
     </row>
-    <row r="407" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:6" ns3:dyDescent="0.2">
       <c r="A407" t="s">
         <v>1</v>
       </c>
-      <c r="B407" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="408" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>NMC622 cathode balance v1. One kg of retained dry cathode paste contains 35.01/39.44 kg oxide, 2.36/39.44 kg carbon black and 2.07/39.44 kg binder; aluminium foil is supplied separately by the parent cell. Dai et al. 2018, Update of Bill-of-Materials and Cathode Materials Production for Lithium-ion Batteries in the GREET Model, Table 8 (BEV NMC622, 108.03 kg cell), https://greet.anl.gov/files/update_bom_cm. Cathode-specific binder and foil split follows the documented parent-cell breakdown: 35.01 kg active oxide, 2.36 kg carbon black, 2.07 kg binder, 5.89 kg aluminium current collector. The NMP process input of 0.0056 kg/kg paste is temporary solvent, excluded from the retained dry-solids sum; its emissions/recovery inventory remains a coverage gap. Existing energy, processing, factory and transport coefficients per kg paste are retained as manufacturing proxies. Their total purchases per kg cell follow the corrected paste demand. The existing polyvinylfluoride binder proxy and the complete-cell material budget remain unvalidated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="408" spans="1:6" ns3:dyDescent="0.2">
       <c r="A408" t="s">
         <v>3</v>
       </c>
@@ -7214,7 +7233,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="409" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:6" ns3:dyDescent="0.2">
       <c r="A409" t="s">
         <v>5</v>
       </c>
@@ -7222,7 +7241,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="410" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:6" ns3:dyDescent="0.2">
       <c r="A410" t="s">
         <v>6</v>
       </c>
@@ -7230,7 +7249,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="411" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:6" ns3:dyDescent="0.2">
       <c r="A411" t="s">
         <v>7</v>
       </c>
@@ -7238,7 +7257,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="412" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:6" ns3:dyDescent="0.2">
       <c r="A412" t="s">
         <v>9</v>
       </c>
@@ -7246,12 +7265,12 @@
         <v>224</v>
       </c>
     </row>
-    <row r="413" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:6" ns3:dyDescent="0.2">
       <c r="A413" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="414" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:6" ns3:dyDescent="0.2">
       <c r="A414" t="s">
         <v>11</v>
       </c>
@@ -7270,8 +7289,13 @@
       <c r="F414" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="415" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="415" spans="1:6" ns3:dyDescent="0.2">
       <c r="A415" t="s">
         <v>212</v>
       </c>
@@ -7291,7 +7315,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="416" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:6" ns3:dyDescent="0.2">
       <c r="A416" t="s">
         <v>124</v>
       </c>
@@ -7311,7 +7335,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="417" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:7" ns3:dyDescent="0.2">
       <c r="A417" t="s">
         <v>55</v>
       </c>
@@ -7331,7 +7355,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="418" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:7" ns3:dyDescent="0.2">
       <c r="A418" t="s">
         <v>61</v>
       </c>
@@ -7351,7 +7375,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="419" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:7" ns3:dyDescent="0.2">
       <c r="A419" t="s">
         <v>45</v>
       </c>
@@ -7371,12 +7395,12 @@
         <v>47</v>
       </c>
     </row>
-    <row r="420" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:7" ns3:dyDescent="0.2">
       <c r="A420" t="s">
         <v>125</v>
       </c>
       <c r="B420" s="4">
-        <v>2.5000000000000001E-2</v>
+        <v>0.059837728194726165</v>
       </c>
       <c r="C420" t="s">
         <v>8</v>
@@ -7390,13 +7414,18 @@
       <c r="F420" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="421" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>NMC622 cathode balance v1. Carbon black: 2.36/(35.01+2.36+2.07) kg/kg dry paste. Dai et al. 2018, Update of Bill-of-Materials and Cathode Materials Production for Lithium-ion Batteries in the GREET Model, Table 8 (BEV NMC622, 108.03 kg cell), https://greet.anl.gov/files/update_bom_cm. Cathode-specific binder and foil split follows the documented parent-cell breakdown: 35.01 kg active oxide, 2.36 kg carbon black, 2.07 kg binder, 5.89 kg aluminium current collector.</t>
+        </is>
+      </c>
+    </row>
+    <row r="421" spans="1:7" ns3:dyDescent="0.2">
       <c r="A421" t="s">
         <v>127</v>
       </c>
       <c r="B421" s="4">
-        <v>2.5000000000000001E-2</v>
+        <v>0.052484787018255576</v>
       </c>
       <c r="C421" t="s">
         <v>8</v>
@@ -7410,8 +7439,13 @@
       <c r="F421" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="422" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>NMC622 cathode balance v1. Binder: 2.07/(35.01+2.36+2.07) kg/kg dry paste. Retains the existing polyvinylfluoride supplier as the source inventory proxy for PVDF; this is not a validated polymer-identity correction. Dai et al. 2018, Update of Bill-of-Materials and Cathode Materials Production for Lithium-ion Batteries in the GREET Model, Table 8 (BEV NMC622, 108.03 kg cell), https://greet.anl.gov/files/update_bom_cm. Cathode-specific binder and foil split follows the documented parent-cell breakdown: 35.01 kg active oxide, 2.36 kg carbon black, 2.07 kg binder, 5.89 kg aluminium current collector.</t>
+        </is>
+      </c>
+    </row>
+    <row r="422" spans="1:7" ns3:dyDescent="0.2">
       <c r="A422" t="s">
         <v>112</v>
       </c>
@@ -7431,7 +7465,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="423" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:7" ns3:dyDescent="0.2">
       <c r="A423" t="s">
         <v>129</v>
       </c>
@@ -7451,7 +7485,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="424" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:7" ns3:dyDescent="0.2">
       <c r="A424" t="s">
         <v>122</v>
       </c>
@@ -7472,12 +7506,12 @@
       </c>
       <c r="G424" s="5"/>
     </row>
-    <row r="425" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:7" ns3:dyDescent="0.2">
       <c r="A425" t="s">
         <v>213</v>
       </c>
       <c r="B425" s="4">
-        <v>0.95</v>
+        <v>0.8876774847870182</v>
       </c>
       <c r="C425" t="s">
         <v>8</v>
@@ -7491,8 +7525,13 @@
       <c r="F425" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="427" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>NMC622 cathode balance v1. Active oxide: 35.01/(35.01+2.36+2.07) kg/kg dry paste. The three retained paste ingredients sum to 1 kg. Dai et al. 2018, Update of Bill-of-Materials and Cathode Materials Production for Lithium-ion Batteries in the GREET Model, Table 8 (BEV NMC622, 108.03 kg cell), https://greet.anl.gov/files/update_bom_cm. Cathode-specific binder and foil split follows the documented parent-cell breakdown: 35.01 kg active oxide, 2.36 kg carbon black, 2.07 kg binder, 5.89 kg aluminium current collector.</t>
+        </is>
+      </c>
+    </row>
+    <row r="427" spans="1:7" ht="16" ns3:dyDescent="0.2">
       <c r="A427" s="2" t="s">
         <v>0</v>
       </c>
@@ -7500,7 +7539,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="428" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:7" ns3:dyDescent="0.2">
       <c r="A428" t="s">
         <v>1</v>
       </c>
@@ -7508,7 +7547,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="429" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:7" ns3:dyDescent="0.2">
       <c r="A429" t="s">
         <v>3</v>
       </c>
@@ -7516,7 +7555,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="430" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="430" spans="1:7" ns3:dyDescent="0.2">
       <c r="A430" t="s">
         <v>5</v>
       </c>
@@ -7524,7 +7563,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="431" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:7" ns3:dyDescent="0.2">
       <c r="A431" t="s">
         <v>6</v>
       </c>
@@ -7532,7 +7571,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="432" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:7" ns3:dyDescent="0.2">
       <c r="A432" t="s">
         <v>7</v>
       </c>
@@ -7540,7 +7579,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="433" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:7" ns3:dyDescent="0.2">
       <c r="A433" t="s">
         <v>9</v>
       </c>
@@ -7548,12 +7587,12 @@
         <v>224</v>
       </c>
     </row>
-    <row r="434" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:7" ns3:dyDescent="0.2">
       <c r="A434" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="435" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:7" ns3:dyDescent="0.2">
       <c r="A435" t="s">
         <v>11</v>
       </c>
@@ -7573,7 +7612,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="436" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:7" ns3:dyDescent="0.2">
       <c r="A436" t="s">
         <v>236</v>
       </c>
@@ -7593,7 +7632,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="437" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:7" ns3:dyDescent="0.2">
       <c r="A437" t="s">
         <v>124</v>
       </c>
@@ -7613,7 +7652,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="438" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:7" ns3:dyDescent="0.2">
       <c r="A438" t="s">
         <v>55</v>
       </c>
@@ -7633,7 +7672,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="439" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:7" ns3:dyDescent="0.2">
       <c r="A439" t="s">
         <v>61</v>
       </c>
@@ -7653,7 +7692,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="440" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="440" spans="1:7" ns3:dyDescent="0.2">
       <c r="A440" t="s">
         <v>45</v>
       </c>
@@ -7673,7 +7712,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="441" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:7" ns3:dyDescent="0.2">
       <c r="A441" t="s">
         <v>125</v>
       </c>
@@ -7693,7 +7732,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="442" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:7" ns3:dyDescent="0.2">
       <c r="A442" t="s">
         <v>127</v>
       </c>
@@ -7713,7 +7752,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="443" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:7" ns3:dyDescent="0.2">
       <c r="A443" t="s">
         <v>112</v>
       </c>
@@ -7733,7 +7772,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="444" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:7" ns3:dyDescent="0.2">
       <c r="A444" t="s">
         <v>129</v>
       </c>
@@ -7753,7 +7792,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="445" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:7" ns3:dyDescent="0.2">
       <c r="A445" t="s">
         <v>122</v>
       </c>
@@ -7774,7 +7813,7 @@
       </c>
       <c r="G445" s="5"/>
     </row>
-    <row r="446" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:7" ns3:dyDescent="0.2">
       <c r="A446" t="s">
         <v>237</v>
       </c>
@@ -7794,7 +7833,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="448" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="448" spans="1:7" ht="16" ns3:dyDescent="0.2">
       <c r="A448" s="2" t="s">
         <v>0</v>
       </c>
@@ -7802,7 +7841,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="449" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="449" spans="1:7" ns3:dyDescent="0.2">
       <c r="A449" t="s">
         <v>1</v>
       </c>
@@ -7810,7 +7849,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="450" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:7" ns3:dyDescent="0.2">
       <c r="A450" t="s">
         <v>3</v>
       </c>
@@ -7818,7 +7857,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="451" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:7" ns3:dyDescent="0.2">
       <c r="A451" t="s">
         <v>5</v>
       </c>
@@ -7826,7 +7865,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="452" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:7" ns3:dyDescent="0.2">
       <c r="A452" t="s">
         <v>6</v>
       </c>
@@ -7834,7 +7873,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="453" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="453" spans="1:7" ns3:dyDescent="0.2">
       <c r="A453" t="s">
         <v>7</v>
       </c>
@@ -7842,7 +7881,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="454" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:7" ns3:dyDescent="0.2">
       <c r="A454" t="s">
         <v>9</v>
       </c>
@@ -7850,12 +7889,12 @@
         <v>224</v>
       </c>
     </row>
-    <row r="455" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="455" spans="1:7" ns3:dyDescent="0.2">
       <c r="A455" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="456" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:7" ns3:dyDescent="0.2">
       <c r="A456" t="s">
         <v>11</v>
       </c>
@@ -7878,7 +7917,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="457" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="457" spans="1:7" ns3:dyDescent="0.2">
       <c r="A457" t="s">
         <v>213</v>
       </c>
@@ -7898,7 +7937,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="458" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="458" spans="1:7" ns3:dyDescent="0.2">
       <c r="A458" t="s">
         <v>124</v>
       </c>
@@ -7918,7 +7957,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="459" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="459" spans="1:7" ns3:dyDescent="0.2">
       <c r="A459" t="s">
         <v>132</v>
       </c>
@@ -7938,7 +7977,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="460" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="460" spans="1:7" ns3:dyDescent="0.2">
       <c r="A460" t="s">
         <v>61</v>
       </c>
@@ -7958,7 +7997,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="461" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:7" ns3:dyDescent="0.2">
       <c r="A461" t="s">
         <v>55</v>
       </c>
@@ -7978,7 +8017,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="462" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="462" spans="1:7" ns3:dyDescent="0.2">
       <c r="A462" t="s">
         <v>45</v>
       </c>
@@ -7998,7 +8037,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="463" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="463" spans="1:7" ns3:dyDescent="0.2">
       <c r="A463" t="s">
         <v>209</v>
       </c>
@@ -8018,7 +8057,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="464" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="464" spans="1:7" ns3:dyDescent="0.2">
       <c r="A464" t="s">
         <v>214</v>
       </c>
@@ -8038,7 +8077,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="465" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="465" spans="1:7" ns3:dyDescent="0.2">
       <c r="A465" t="s">
         <v>122</v>
       </c>
@@ -8058,7 +8097,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="466" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="466" spans="1:7" ns3:dyDescent="0.2">
       <c r="A466" t="s">
         <v>134</v>
       </c>
@@ -8075,7 +8114,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="467" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="467" spans="1:7" ns3:dyDescent="0.2">
       <c r="A467" t="s">
         <v>137</v>
       </c>
@@ -8092,10 +8131,10 @@
         <v>136</v>
       </c>
     </row>
-    <row r="468" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="468" spans="1:7" ns3:dyDescent="0.2">
       <c r="G468" s="5"/>
     </row>
-    <row r="469" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="469" spans="1:7" ht="16" ns3:dyDescent="0.2">
       <c r="A469" s="2" t="s">
         <v>0</v>
       </c>
@@ -8103,7 +8142,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="470" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="470" spans="1:7" ns3:dyDescent="0.2">
       <c r="A470" t="s">
         <v>1</v>
       </c>
@@ -8111,7 +8150,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="471" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="471" spans="1:7" ns3:dyDescent="0.2">
       <c r="A471" t="s">
         <v>3</v>
       </c>
@@ -8119,7 +8158,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="472" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="472" spans="1:7" ns3:dyDescent="0.2">
       <c r="A472" t="s">
         <v>5</v>
       </c>
@@ -8127,7 +8166,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="473" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="473" spans="1:7" ns3:dyDescent="0.2">
       <c r="A473" t="s">
         <v>6</v>
       </c>
@@ -8135,7 +8174,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="474" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="474" spans="1:7" ns3:dyDescent="0.2">
       <c r="A474" t="s">
         <v>7</v>
       </c>
@@ -8143,7 +8182,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="475" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="475" spans="1:7" ns3:dyDescent="0.2">
       <c r="A475" t="s">
         <v>9</v>
       </c>
@@ -8151,12 +8190,12 @@
         <v>238</v>
       </c>
     </row>
-    <row r="476" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="476" spans="1:7" ns3:dyDescent="0.2">
       <c r="A476" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="477" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="477" spans="1:7" ns3:dyDescent="0.2">
       <c r="A477" t="s">
         <v>11</v>
       </c>
@@ -8179,7 +8218,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="478" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="478" spans="1:7" ns3:dyDescent="0.2">
       <c r="A478" t="s">
         <v>237</v>
       </c>
@@ -8199,7 +8238,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="479" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="479" spans="1:7" ns3:dyDescent="0.2">
       <c r="A479" t="s">
         <v>124</v>
       </c>
@@ -8219,7 +8258,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="480" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="480" spans="1:7" ns3:dyDescent="0.2">
       <c r="A480" t="s">
         <v>132</v>
       </c>
@@ -8239,7 +8278,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="481" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="481" spans="1:7" ns3:dyDescent="0.2">
       <c r="A481" t="s">
         <v>61</v>
       </c>
@@ -8259,7 +8298,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="482" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="482" spans="1:7" ns3:dyDescent="0.2">
       <c r="A482" t="s">
         <v>55</v>
       </c>
@@ -8279,7 +8318,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="483" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="483" spans="1:7" ns3:dyDescent="0.2">
       <c r="A483" t="s">
         <v>45</v>
       </c>
@@ -8299,7 +8338,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="484" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="484" spans="1:7" ns3:dyDescent="0.2">
       <c r="A484" t="s">
         <v>209</v>
       </c>
@@ -8319,7 +8358,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="485" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="485" spans="1:7" ns3:dyDescent="0.2">
       <c r="A485" t="s">
         <v>239</v>
       </c>
@@ -8339,7 +8378,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="486" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="486" spans="1:7" ns3:dyDescent="0.2">
       <c r="A486" t="s">
         <v>122</v>
       </c>
@@ -8359,7 +8398,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="487" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="487" spans="1:7" ns3:dyDescent="0.2">
       <c r="A487" t="s">
         <v>134</v>
       </c>
@@ -8376,7 +8415,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="488" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="488" spans="1:7" ns3:dyDescent="0.2">
       <c r="A488" t="s">
         <v>137</v>
       </c>
@@ -8393,10 +8432,10 @@
         <v>136</v>
       </c>
     </row>
-    <row r="489" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="489" spans="1:7" ns3:dyDescent="0.2">
       <c r="G489" s="5"/>
     </row>
-    <row r="490" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="490" spans="1:7" ht="16" ns3:dyDescent="0.2">
       <c r="A490" s="2" t="s">
         <v>0</v>
       </c>
@@ -8404,7 +8443,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="491" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="491" spans="1:7" ns3:dyDescent="0.2">
       <c r="A491" t="s">
         <v>1</v>
       </c>
@@ -8412,7 +8451,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="492" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="492" spans="1:7" ns3:dyDescent="0.2">
       <c r="A492" t="s">
         <v>3</v>
       </c>
@@ -8420,7 +8459,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="493" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="493" spans="1:7" ns3:dyDescent="0.2">
       <c r="A493" t="s">
         <v>5</v>
       </c>
@@ -8428,7 +8467,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="494" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="494" spans="1:7" ns3:dyDescent="0.2">
       <c r="A494" t="s">
         <v>6</v>
       </c>
@@ -8436,7 +8475,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="495" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="495" spans="1:7" ns3:dyDescent="0.2">
       <c r="A495" t="s">
         <v>7</v>
       </c>
@@ -8444,7 +8483,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="496" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="496" spans="1:7" ns3:dyDescent="0.2">
       <c r="A496" t="s">
         <v>9</v>
       </c>
@@ -8452,12 +8491,12 @@
         <v>224</v>
       </c>
     </row>
-    <row r="497" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="497" spans="1:14" ns3:dyDescent="0.2">
       <c r="A497" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="498" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="498" spans="1:14" ns3:dyDescent="0.2">
       <c r="A498" t="s">
         <v>11</v>
       </c>
@@ -8480,7 +8519,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="499" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="499" spans="1:14" ns3:dyDescent="0.2">
       <c r="A499" t="s">
         <v>214</v>
       </c>
@@ -8500,7 +8539,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="500" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="500" spans="1:14" ns3:dyDescent="0.2">
       <c r="A500" t="s">
         <v>132</v>
       </c>
@@ -8520,7 +8559,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="501" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="501" spans="1:14" ns3:dyDescent="0.2">
       <c r="A501" t="s">
         <v>55</v>
       </c>
@@ -8540,7 +8579,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="502" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="502" spans="1:14" ns3:dyDescent="0.2">
       <c r="A502" t="s">
         <v>124</v>
       </c>
@@ -8560,7 +8599,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="503" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="503" spans="1:14" ns3:dyDescent="0.2">
       <c r="A503" t="s">
         <v>61</v>
       </c>
@@ -8580,7 +8619,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="504" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="504" spans="1:14" ns3:dyDescent="0.2">
       <c r="A504" t="s">
         <v>112</v>
       </c>
@@ -8600,7 +8639,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="505" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="505" spans="1:14" ns3:dyDescent="0.2">
       <c r="A505" t="s">
         <v>141</v>
       </c>
@@ -8620,7 +8659,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="506" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="506" spans="1:14" ns3:dyDescent="0.2">
       <c r="A506" t="s">
         <v>208</v>
       </c>
@@ -8640,7 +8679,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="507" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="507" spans="1:14" ns3:dyDescent="0.2">
       <c r="A507" t="s">
         <v>144</v>
       </c>
@@ -8660,7 +8699,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="508" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="508" spans="1:14" ns3:dyDescent="0.2">
       <c r="A508" t="s">
         <v>146</v>
       </c>
@@ -8680,7 +8719,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="509" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="509" spans="1:14" ns3:dyDescent="0.2">
       <c r="A509" t="s">
         <v>148</v>
       </c>
@@ -8701,7 +8740,7 @@
       </c>
       <c r="N509" s="8"/>
     </row>
-    <row r="510" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="510" spans="1:14" ns3:dyDescent="0.2">
       <c r="A510" t="s">
         <v>122</v>
       </c>
@@ -8721,7 +8760,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="511" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="511" spans="1:14" ns3:dyDescent="0.2">
       <c r="A511" t="s">
         <v>150</v>
       </c>
@@ -8741,7 +8780,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="512" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="512" spans="1:14" ns3:dyDescent="0.2">
       <c r="A512" t="s">
         <v>152</v>
       </c>
@@ -8758,7 +8797,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="513" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="513" spans="1:24" ns3:dyDescent="0.2">
       <c r="A513" t="s">
         <v>153</v>
       </c>
@@ -8775,7 +8814,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="515" spans="1:24" ht="16" x14ac:dyDescent="0.2">
+    <row r="515" spans="1:24" ht="16" ns3:dyDescent="0.2">
       <c r="A515" s="2" t="s">
         <v>0</v>
       </c>
@@ -8783,7 +8822,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="516" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="516" spans="1:24" ns3:dyDescent="0.2">
       <c r="A516" t="s">
         <v>1</v>
       </c>
@@ -8791,7 +8830,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="517" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="517" spans="1:24" ns3:dyDescent="0.2">
       <c r="A517" t="s">
         <v>3</v>
       </c>
@@ -8799,7 +8838,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="518" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="518" spans="1:24" ns3:dyDescent="0.2">
       <c r="A518" t="s">
         <v>5</v>
       </c>
@@ -8807,7 +8846,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="519" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="519" spans="1:24" ns3:dyDescent="0.2">
       <c r="A519" t="s">
         <v>6</v>
       </c>
@@ -8815,7 +8854,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="520" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="520" spans="1:24" ns3:dyDescent="0.2">
       <c r="A520" t="s">
         <v>7</v>
       </c>
@@ -8823,7 +8862,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="521" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="521" spans="1:24" ns3:dyDescent="0.2">
       <c r="A521" t="s">
         <v>9</v>
       </c>
@@ -8831,12 +8870,12 @@
         <v>225</v>
       </c>
     </row>
-    <row r="522" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="522" spans="1:24" ns3:dyDescent="0.2">
       <c r="A522" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="523" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="523" spans="1:24" ns3:dyDescent="0.2">
       <c r="A523" t="s">
         <v>11</v>
       </c>
@@ -8859,7 +8898,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="524" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="524" spans="1:24" ns3:dyDescent="0.2">
       <c r="A524" t="s">
         <v>239</v>
       </c>
@@ -8879,7 +8918,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="525" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="525" spans="1:24" ns3:dyDescent="0.2">
       <c r="A525" t="s">
         <v>132</v>
       </c>
@@ -8899,7 +8938,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="526" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="526" spans="1:24" ns3:dyDescent="0.2">
       <c r="A526" t="s">
         <v>55</v>
       </c>
@@ -8919,7 +8958,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="527" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="527" spans="1:24" ns3:dyDescent="0.2">
       <c r="A527" t="s">
         <v>124</v>
       </c>
@@ -8942,7 +8981,7 @@
       <c r="S527" s="5"/>
       <c r="X527" s="5"/>
     </row>
-    <row r="528" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="528" spans="1:24" ns3:dyDescent="0.2">
       <c r="A528" t="s">
         <v>61</v>
       </c>
@@ -8962,7 +9001,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="529" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="529" spans="1:14" ns3:dyDescent="0.2">
       <c r="A529" t="s">
         <v>112</v>
       </c>
@@ -8982,7 +9021,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="530" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="530" spans="1:14" ns3:dyDescent="0.2">
       <c r="A530" t="s">
         <v>141</v>
       </c>
@@ -9002,7 +9041,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="531" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="531" spans="1:14" ns3:dyDescent="0.2">
       <c r="A531" t="s">
         <v>208</v>
       </c>
@@ -9022,7 +9061,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="532" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="532" spans="1:14" ns3:dyDescent="0.2">
       <c r="A532" t="s">
         <v>144</v>
       </c>
@@ -9042,7 +9081,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="533" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="533" spans="1:14" ns3:dyDescent="0.2">
       <c r="A533" t="s">
         <v>146</v>
       </c>
@@ -9062,7 +9101,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="534" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="534" spans="1:14" ns3:dyDescent="0.2">
       <c r="A534" t="s">
         <v>148</v>
       </c>
@@ -9083,7 +9122,7 @@
       </c>
       <c r="N534" s="8"/>
     </row>
-    <row r="535" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="535" spans="1:14" ns3:dyDescent="0.2">
       <c r="A535" t="s">
         <v>122</v>
       </c>
@@ -9103,7 +9142,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="536" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="536" spans="1:14" ns3:dyDescent="0.2">
       <c r="A536" t="s">
         <v>150</v>
       </c>
@@ -9123,7 +9162,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="537" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="537" spans="1:14" ns3:dyDescent="0.2">
       <c r="A537" t="s">
         <v>152</v>
       </c>
@@ -9140,7 +9179,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="538" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="538" spans="1:14" ns3:dyDescent="0.2">
       <c r="A538" t="s">
         <v>153</v>
       </c>
@@ -9157,7 +9196,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="540" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="540" spans="1:14" ht="16" ns3:dyDescent="0.2">
       <c r="A540" s="2" t="s">
         <v>0</v>
       </c>
@@ -9165,7 +9204,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="541" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="541" spans="1:14" ns3:dyDescent="0.2">
       <c r="A541" t="s">
         <v>1</v>
       </c>
@@ -9173,7 +9212,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="542" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="542" spans="1:14" ns3:dyDescent="0.2">
       <c r="A542" t="s">
         <v>3</v>
       </c>
@@ -9181,7 +9220,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="543" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="543" spans="1:14" ns3:dyDescent="0.2">
       <c r="A543" t="s">
         <v>5</v>
       </c>
@@ -9189,7 +9228,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="544" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="544" spans="1:14" ns3:dyDescent="0.2">
       <c r="A544" t="s">
         <v>6</v>
       </c>
@@ -9197,7 +9236,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="545" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="545" spans="1:11" ns3:dyDescent="0.2">
       <c r="A545" t="s">
         <v>7</v>
       </c>
@@ -9205,7 +9244,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="546" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="546" spans="1:11" ns3:dyDescent="0.2">
       <c r="A546" t="s">
         <v>9</v>
       </c>
@@ -9213,12 +9252,12 @@
         <v>180</v>
       </c>
     </row>
-    <row r="547" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="547" spans="1:11" ns3:dyDescent="0.2">
       <c r="A547" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="548" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="548" spans="1:11" ns3:dyDescent="0.2">
       <c r="A548" t="s">
         <v>11</v>
       </c>
@@ -9241,7 +9280,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="549" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="549" spans="1:11" ns3:dyDescent="0.2">
       <c r="A549" t="s">
         <v>157</v>
       </c>
@@ -9261,7 +9300,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="550" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="550" spans="1:11" ns3:dyDescent="0.2">
       <c r="A550" t="s">
         <v>61</v>
       </c>
@@ -9281,7 +9320,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="551" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="551" spans="1:11" ns3:dyDescent="0.2">
       <c r="A551" t="s">
         <v>55</v>
       </c>
@@ -9301,7 +9340,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="552" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="552" spans="1:11" ns3:dyDescent="0.2">
       <c r="A552" t="s">
         <v>59</v>
       </c>
@@ -9321,7 +9360,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="553" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="553" spans="1:11" ns3:dyDescent="0.2">
       <c r="A553" t="s">
         <v>181</v>
       </c>
@@ -9341,7 +9380,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="554" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="554" spans="1:11" ns3:dyDescent="0.2">
       <c r="A554" t="s">
         <v>182</v>
       </c>
@@ -9361,7 +9400,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="555" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="555" spans="1:11" ns3:dyDescent="0.2">
       <c r="A555" t="s">
         <v>45</v>
       </c>
@@ -9381,7 +9420,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="556" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="556" spans="1:11" ns3:dyDescent="0.2">
       <c r="A556" t="s">
         <v>122</v>
       </c>
@@ -9401,7 +9440,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="557" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="557" spans="1:11" ns3:dyDescent="0.2">
       <c r="A557" t="s">
         <v>183</v>
       </c>
@@ -9421,7 +9460,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="558" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="558" spans="1:11" ns3:dyDescent="0.2">
       <c r="A558" t="s">
         <v>186</v>
       </c>
@@ -9441,7 +9480,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="559" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="559" spans="1:11" ns3:dyDescent="0.2">
       <c r="A559" t="s">
         <v>158</v>
       </c>
@@ -9462,7 +9501,7 @@
       </c>
       <c r="K559" s="5"/>
     </row>
-    <row r="560" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="560" spans="1:11" ns3:dyDescent="0.2">
       <c r="A560" t="s">
         <v>184</v>
       </c>
@@ -9482,7 +9521,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="561" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="561" spans="1:11" ns3:dyDescent="0.2">
       <c r="A561" t="s">
         <v>184</v>
       </c>
@@ -9502,7 +9541,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="562" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="562" spans="1:11" ns3:dyDescent="0.2">
       <c r="A562" t="s">
         <v>150</v>
       </c>
@@ -9522,7 +9561,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="563" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="563" spans="1:11" ns3:dyDescent="0.2">
       <c r="A563" t="s">
         <v>150</v>
       </c>
@@ -9542,7 +9581,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="564" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="564" spans="1:11" ns3:dyDescent="0.2">
       <c r="A564" t="s">
         <v>150</v>
       </c>
@@ -9562,7 +9601,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="565" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="565" spans="1:11" ns3:dyDescent="0.2">
       <c r="A565" t="s">
         <v>188</v>
       </c>
@@ -9583,7 +9622,7 @@
       </c>
       <c r="K565" s="5"/>
     </row>
-    <row r="566" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="566" spans="1:11" ns3:dyDescent="0.2">
       <c r="A566" t="s">
         <v>188</v>
       </c>
@@ -9604,7 +9643,7 @@
       </c>
       <c r="K566" s="5"/>
     </row>
-    <row r="567" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="567" spans="1:11" ns3:dyDescent="0.2">
       <c r="A567" t="s">
         <v>190</v>
       </c>
@@ -9625,7 +9664,7 @@
       </c>
       <c r="K567" s="5"/>
     </row>
-    <row r="568" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="568" spans="1:11" ns3:dyDescent="0.2">
       <c r="A568" t="s">
         <v>190</v>
       </c>
@@ -9645,7 +9684,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="570" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="570" spans="1:11" ht="16" ns3:dyDescent="0.2">
       <c r="A570" s="2" t="s">
         <v>0</v>
       </c>
@@ -9653,7 +9692,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="571" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="571" spans="1:11" ns3:dyDescent="0.2">
       <c r="A571" t="s">
         <v>1</v>
       </c>
@@ -9661,7 +9700,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="572" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="572" spans="1:11" ns3:dyDescent="0.2">
       <c r="A572" t="s">
         <v>3</v>
       </c>
@@ -9669,7 +9708,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="573" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="573" spans="1:11" ns3:dyDescent="0.2">
       <c r="A573" t="s">
         <v>5</v>
       </c>
@@ -9677,7 +9716,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="574" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="574" spans="1:11" ns3:dyDescent="0.2">
       <c r="A574" t="s">
         <v>6</v>
       </c>
@@ -9685,7 +9724,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="575" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="575" spans="1:11" ns3:dyDescent="0.2">
       <c r="A575" t="s">
         <v>7</v>
       </c>
@@ -9693,7 +9732,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="576" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="576" spans="1:11" ns3:dyDescent="0.2">
       <c r="A576" t="s">
         <v>195</v>
       </c>
@@ -9701,12 +9740,12 @@
         <v>193</v>
       </c>
     </row>
-    <row r="577" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="577" spans="1:8" ht="16" ns3:dyDescent="0.2">
       <c r="A577" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="578" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="578" spans="1:8" ns3:dyDescent="0.2">
       <c r="A578" t="s">
         <v>11</v>
       </c>
@@ -9726,7 +9765,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="579" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="579" spans="1:8" ns3:dyDescent="0.2">
       <c r="A579" t="s">
         <v>194</v>
       </c>
@@ -9746,7 +9785,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="580" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="580" spans="1:8" ns3:dyDescent="0.2">
       <c r="A580" t="s">
         <v>196</v>
       </c>
@@ -9766,7 +9805,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="581" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="581" spans="1:8" ns3:dyDescent="0.2">
       <c r="A581" t="s">
         <v>197</v>
       </c>
@@ -9786,7 +9825,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="582" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="582" spans="1:8" ns3:dyDescent="0.2">
       <c r="A582" t="s">
         <v>198</v>
       </c>
@@ -9806,7 +9845,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="584" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="584" spans="1:8" ht="16" ns3:dyDescent="0.2">
       <c r="A584" s="2" t="s">
         <v>0</v>
       </c>
@@ -9814,7 +9853,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="585" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="585" spans="1:8" ns3:dyDescent="0.2">
       <c r="A585" t="s">
         <v>1</v>
       </c>
@@ -9822,7 +9861,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="586" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="586" spans="1:8" ns3:dyDescent="0.2">
       <c r="A586" t="s">
         <v>3</v>
       </c>
@@ -9830,7 +9869,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="587" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="587" spans="1:8" ns3:dyDescent="0.2">
       <c r="A587" t="s">
         <v>5</v>
       </c>
@@ -9838,7 +9877,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="588" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="588" spans="1:8" ns3:dyDescent="0.2">
       <c r="A588" t="s">
         <v>6</v>
       </c>
@@ -9846,7 +9885,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="589" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="589" spans="1:8" ns3:dyDescent="0.2">
       <c r="A589" t="s">
         <v>7</v>
       </c>
@@ -9854,7 +9893,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="590" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="590" spans="1:8" ns3:dyDescent="0.2">
       <c r="A590" t="s">
         <v>195</v>
       </c>
@@ -9862,12 +9901,12 @@
         <v>193</v>
       </c>
     </row>
-    <row r="591" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="591" spans="1:8" ht="16" ns3:dyDescent="0.2">
       <c r="A591" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="592" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="592" spans="1:8" ns3:dyDescent="0.2">
       <c r="A592" t="s">
         <v>11</v>
       </c>
@@ -9893,7 +9932,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="593" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="593" spans="1:8" ns3:dyDescent="0.2">
       <c r="A593" t="s">
         <v>196</v>
       </c>
@@ -9913,7 +9952,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="594" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="594" spans="1:8" ns3:dyDescent="0.2">
       <c r="A594" t="s">
         <v>200</v>
       </c>
@@ -9936,7 +9975,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="595" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="595" spans="1:8" ns3:dyDescent="0.2">
       <c r="A595" t="s">
         <v>167</v>
       </c>
@@ -9959,7 +9998,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="596" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="596" spans="1:8" ns3:dyDescent="0.2">
       <c r="A596" t="s">
         <v>35</v>
       </c>
@@ -9982,7 +10021,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="597" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="597" spans="1:8" ns3:dyDescent="0.2">
       <c r="A597" t="s">
         <v>98</v>
       </c>
@@ -10005,7 +10044,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="598" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="598" spans="1:8" ns3:dyDescent="0.2">
       <c r="A598" t="s">
         <v>202</v>
       </c>
@@ -10028,7 +10067,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="599" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="599" spans="1:8" ns3:dyDescent="0.2">
       <c r="A599" t="s">
         <v>204</v>
       </c>
@@ -10051,7 +10090,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="600" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="600" spans="1:8" ns3:dyDescent="0.2">
       <c r="A600" t="s">
         <v>85</v>
       </c>
@@ -10077,7 +10116,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="601" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="601" spans="1:8" ns3:dyDescent="0.2">
       <c r="A601" t="s">
         <v>120</v>
       </c>
@@ -10100,7 +10139,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="602" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="602" spans="1:8" ns3:dyDescent="0.2">
       <c r="A602" t="s">
         <v>39</v>
       </c>
@@ -10123,7 +10162,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="604" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="604" spans="1:8" ht="16" ns3:dyDescent="0.2">
       <c r="A604" s="2" t="s">
         <v>0</v>
       </c>
@@ -10131,7 +10170,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="605" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="605" spans="1:8" ns3:dyDescent="0.2">
       <c r="A605" t="s">
         <v>1</v>
       </c>
@@ -10139,7 +10178,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="606" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="606" spans="1:8" ns3:dyDescent="0.2">
       <c r="A606" t="s">
         <v>3</v>
       </c>
@@ -10147,7 +10186,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="607" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="607" spans="1:8" ns3:dyDescent="0.2">
       <c r="A607" t="s">
         <v>5</v>
       </c>
@@ -10155,7 +10194,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="608" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="608" spans="1:8" ns3:dyDescent="0.2">
       <c r="A608" t="s">
         <v>6</v>
       </c>
@@ -10163,7 +10202,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="609" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="609" spans="1:7" ns3:dyDescent="0.2">
       <c r="A609" t="s">
         <v>7</v>
       </c>
@@ -10171,7 +10210,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="610" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="610" spans="1:7" ns3:dyDescent="0.2">
       <c r="A610" t="s">
         <v>195</v>
       </c>
@@ -10179,12 +10218,12 @@
         <v>193</v>
       </c>
     </row>
-    <row r="611" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="611" spans="1:7" ht="16" ns3:dyDescent="0.2">
       <c r="A611" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="612" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="612" spans="1:7" ns3:dyDescent="0.2">
       <c r="A612" t="s">
         <v>11</v>
       </c>
@@ -10207,7 +10246,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="613" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="613" spans="1:7" ns3:dyDescent="0.2">
       <c r="A613" t="s">
         <v>197</v>
       </c>
@@ -10227,7 +10266,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="614" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="614" spans="1:7" ns3:dyDescent="0.2">
       <c r="A614" t="s">
         <v>200</v>
       </c>
@@ -10250,7 +10289,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="615" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="615" spans="1:7" ns3:dyDescent="0.2">
       <c r="A615" t="s">
         <v>167</v>
       </c>
@@ -10273,7 +10312,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="616" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="616" spans="1:7" ns3:dyDescent="0.2">
       <c r="A616" t="s">
         <v>39</v>
       </c>
@@ -10296,7 +10335,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="618" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="618" spans="1:7" ht="16" ns3:dyDescent="0.2">
       <c r="A618" s="2" t="s">
         <v>0</v>
       </c>
@@ -10304,7 +10343,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="619" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="619" spans="1:7" ns3:dyDescent="0.2">
       <c r="A619" t="s">
         <v>1</v>
       </c>
@@ -10312,7 +10351,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="620" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="620" spans="1:7" ns3:dyDescent="0.2">
       <c r="A620" t="s">
         <v>3</v>
       </c>
@@ -10320,7 +10359,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="621" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="621" spans="1:7" ns3:dyDescent="0.2">
       <c r="A621" t="s">
         <v>5</v>
       </c>
@@ -10328,7 +10367,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="622" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="622" spans="1:7" ns3:dyDescent="0.2">
       <c r="A622" t="s">
         <v>6</v>
       </c>
@@ -10336,7 +10375,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="623" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="623" spans="1:7" ns3:dyDescent="0.2">
       <c r="A623" t="s">
         <v>7</v>
       </c>
@@ -10344,7 +10383,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="624" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="624" spans="1:7" ns3:dyDescent="0.2">
       <c r="A624" t="s">
         <v>195</v>
       </c>
@@ -10352,12 +10391,12 @@
         <v>193</v>
       </c>
     </row>
-    <row r="625" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="625" spans="1:7" ht="16" ns3:dyDescent="0.2">
       <c r="A625" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="626" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="626" spans="1:7" ns3:dyDescent="0.2">
       <c r="A626" t="s">
         <v>11</v>
       </c>
@@ -10380,7 +10419,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="627" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="627" spans="1:7" ns3:dyDescent="0.2">
       <c r="A627" t="s">
         <v>198</v>
       </c>
@@ -10400,7 +10439,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="628" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="628" spans="1:7" ns3:dyDescent="0.2">
       <c r="A628" t="s">
         <v>41</v>
       </c>
@@ -10423,7 +10462,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="629" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="629" spans="1:7" ns3:dyDescent="0.2">
       <c r="A629" t="s">
         <v>50</v>
       </c>
@@ -10446,7 +10485,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="630" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="630" spans="1:7" ns3:dyDescent="0.2">
       <c r="A630" t="s">
         <v>43</v>
       </c>
@@ -10470,8 +10509,8 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:X677" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:X677" ns2:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" ns4:id="rId1"/>
 </worksheet>
 </file>
--- a/premise/data/additional_inventories/lci-batteries-NMC622-NMC532.xlsx
+++ b/premise/data/additional_inventories/lci-batteries-NMC622-NMC532.xlsx
@@ -1165,7 +1165,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:ns4="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X630"/>
+  <dimension ref="A1:X643"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" ns3:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="74.1640625" customWidth="1"/>
@@ -10508,6 +10508,197 @@
         <v>44</v>
       </c>
     </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>market for battery cell, Li-ion, NMC532</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B635">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>battery cell, Li-ion, NMC532</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split.</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Supply alias for the existing public supplemental NMC532 cell production in ecoinvent3.8-3.10; native cell market takes over when this supplement is skipped in3.11+.</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E641" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F641" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G641" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H641" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>market for battery cell, Li-ion, NMC532</t>
+        </is>
+      </c>
+      <c r="B642">
+        <v>1</v>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F642" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G642" t="inlineStr">
+        <is>
+          <t>battery cell, Li-ion, NMC532</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>battery cell production, Li-ion, NMC532</t>
+        </is>
+      </c>
+      <c r="B643">
+        <v>1</v>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F643" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G643" t="inlineStr">
+        <is>
+          <t>battery cell, Li-ion, NMC532</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:X677" ns2:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/premise/data/additional_inventories/lci-batteries-NMC622-NMC532.xlsx
+++ b/premise/data/additional_inventories/lci-batteries-NMC622-NMC532.xlsx
@@ -16,7 +16,7 @@
     <sheet name="Battery - NMC" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Battery - NMC'!$A$1:$X$677</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Battery - NMC'!$A$1:$X$678</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1165,7 +1165,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:ns4="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X643"/>
+  <dimension ref="A1:X644"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" ns3:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="74.1640625" customWidth="1"/>
@@ -10516,7 +10516,7 @@
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>market for battery cell, Li-ion, NMC532</t>
+          <t xml:space="preserve">market for battery cell, lithium-ion, nmc532</t>
         </is>
       </c>
     </row>
@@ -10593,86 +10593,68 @@
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>Exchanges</t>
+          <t xml:space="preserve">type</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t xml:space="preserve">processwithreferenceproduct</t>
         </is>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
           <t>name</t>
         </is>
       </c>
-      <c r="B641" t="inlineStr">
+      <c r="B642" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="C641" t="inlineStr">
+      <c r="C642" t="inlineStr">
         <is>
           <t>location</t>
         </is>
       </c>
-      <c r="D641" t="inlineStr">
+      <c r="D642" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="E641" t="inlineStr">
+      <c r="E642" t="inlineStr">
         <is>
           <t>categories</t>
         </is>
       </c>
-      <c r="F641" t="inlineStr">
+      <c r="F642" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="G641" t="inlineStr">
+      <c r="G642" t="inlineStr">
         <is>
           <t>reference product</t>
         </is>
       </c>
-      <c r="H641" t="inlineStr">
+      <c r="H642" t="inlineStr">
         <is>
           <t>comment</t>
         </is>
       </c>
     </row>
-    <row r="642">
-      <c r="A642" t="inlineStr">
-        <is>
-          <t>market for battery cell, Li-ion, NMC532</t>
-        </is>
-      </c>
-      <c r="B642">
-        <v>1</v>
-      </c>
-      <c r="C642" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D642" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F642" t="inlineStr">
-        <is>
-          <t>production</t>
-        </is>
-      </c>
-      <c r="G642" t="inlineStr">
-        <is>
-          <t>battery cell, Li-ion, NMC532</t>
-        </is>
-      </c>
-    </row>
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>battery cell production, Li-ion, NMC532</t>
+          <t xml:space="preserve">market for battery cell, lithium-ion, nmc532</t>
         </is>
       </c>
       <c r="B643">
@@ -10690,7 +10672,7 @@
       </c>
       <c r="F643" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t>production</t>
         </is>
       </c>
       <c r="G643" t="inlineStr">
@@ -10699,8 +10681,38 @@
         </is>
       </c>
     </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>battery cell production, Li-ion, NMC532</t>
+        </is>
+      </c>
+      <c r="B644">
+        <v>1</v>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F644" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G644" t="inlineStr">
+        <is>
+          <t>battery cell, Li-ion, NMC532</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:X677" ns2:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:X678" ns2:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" ns4:id="rId1"/>
 </worksheet>
